--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,275 +1009,275 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>12.42</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-37.02</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-104.01</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4342197.268786128</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1361673.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1178368.2</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>876208.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>758152.44</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>302159</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>41662.17113525204</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>102422.58</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>19.29</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>12.4</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-80.76</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-103.64</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>4345525.326338639</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>98400.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>983189.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>768634.0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>737617.34</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>214555</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>30614.82493160136</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>74825.17</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-69.65395492947597</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-79.3848243622769</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-18.95988124871053</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>12.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>149.527</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,57 +1440,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-134.75</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-103.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1173448.8</t>
+          <t>983189.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>813852.9</t>
+          <t>768634.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>742038.84</t>
+          <t>737617.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>22576.57974837472</t>
+          <t>30614.82493160136</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>168078.66</v>
+        <v>74825.17</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,27 +1613,27 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>190.257</t>
+          <t>149.527</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,52 +1871,52 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-210.39</t>
+          <t>-134.75</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.92</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2316222.0</t>
+          <t>1828476.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>919222.4</t>
+          <t>1173448.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>656614.8</t>
+          <t>813852.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>708081.34</t>
+          <t>742038.84</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>262607</t>
+          <t>359595</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3878.344779343355</t>
+          <t>22576.57974837472</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>109929.84</v>
+        <v>168078.66</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.042</t>
+          <t>190.257</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,37 +2322,37 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-427.83</t>
+          <t>-210.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-101.92</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>287070.0</t>
+          <t>2316222.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>536609.4</t>
+          <t>919222.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>526455.8</t>
+          <t>656614.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>668527.98</t>
+          <t>708081.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>262607</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-24570.74249267402</t>
+          <t>-3878.344779343355</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-29324.47</v>
+        <v>109929.84</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,27 +2475,27 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>23.042</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,42 +2733,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-7719.21</t>
+          <t>-427.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,205 +2803,205 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-100.91</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>4342197.268786128</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>287070.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>536609.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>526455.8</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>668527.98</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-24570.74249267402</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-29324.47</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-99.94</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>4345525.326338639</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>385780.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>574049.2</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>513642.2</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>677934.64</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>60406</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-23706.4286024678</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-9802.75</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>19.29</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
         <is>
           <t>12.35</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-69.65395492947597</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-79.3848243622769</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-18.95988124871053</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>12.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>86.144</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>12.38</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>12.36</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-553.19</t>
+          <t>-7719.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-98.71</t>
+          <t>-99.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1049696.0</t>
+          <t>385780.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>554078.4</t>
+          <t>574049.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>549015.7</t>
+          <t>513642.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>681025.48</t>
+          <t>677934.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-26234.36937883106</t>
+          <t>-23706.4286024678</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>7859.44</v>
+        <v>-9802.75</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,32 +3337,32 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.054</t>
+          <t>86.144</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,47 +3595,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-243.89</t>
+          <t>-553.19</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.93</t>
+          <t>-98.71</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>557344.0</t>
+          <t>1049696.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>454257.0</t>
+          <t>554078.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>459605.5</t>
+          <t>549015.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>684653.76</t>
+          <t>681025.48</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-32433.24313132533</t>
+          <t>-26234.36937883106</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-38323.41</v>
+        <v>7859.44</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,22 +3768,22 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33.103</t>
+          <t>46.054</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.61</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,47 +4026,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4081,22 +4081,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-130.21</t>
+          <t>-243.89</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-95.06</t>
+          <t>-96.93</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>403157.0</t>
+          <t>557344.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>394007.2</t>
+          <t>454257.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>461441.1</t>
+          <t>459605.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>674235.88</t>
+          <t>684653.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-67433</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-31362.30293904196</t>
+          <t>-32433.24313132533</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-50178.22</v>
+        <v>-38323.41</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>38.499</t>
+          <t>33.103</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,37 +4472,37 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-57.50</t>
+          <t>-130.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-93.45</t>
+          <t>-95.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>474269.0</t>
+          <t>403157.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>516302.2</t>
+          <t>394007.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>609210.8</t>
+          <t>461441.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>687313.42</t>
+          <t>674235.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-92908</t>
+          <t>-67433</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-27941.22684321377</t>
+          <t>-31362.30293904196</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-48801.55</v>
+        <v>-50178.22</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,32 +4630,32 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23.043</t>
+          <t>38.499</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,69 +4772,69 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-15.25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-22.13</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,275 +4888,275 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>12.37</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-57.50</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-93.45</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>4342197.268786128</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>474269.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>516302.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>609210.8</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>687313.42</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-92908</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-27941.22684321377</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-48801.55</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>12.59</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-32.41</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-92.51</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>4345525.326338639</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>285926.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>453235.2</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>582058.9</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>679543.52</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-128823</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-24148.44165449194</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-52711.1</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>19.29</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
         <is>
           <t>12.35</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-69.65395492947597</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-79.3848243622769</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-18.95988124871053</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>9.69</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>12.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.064</t>
+          <t>23.043</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-22.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,42 +5319,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-32.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4345525.326338639</t>
+          <t>4342197.268786128</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>550589.0</t>
+          <t>285926.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>543953.0</t>
+          <t>453235.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>574127.8</t>
+          <t>582058.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>681507.36</t>
+          <t>679543.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-30174</t>
+          <t>-128823</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-18955.23181313051</t>
+          <t>-24148.44165449194</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-36234.02</v>
+        <v>-52711.1</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-69.65395492947597</t>
+          <t>213.791452172872</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-79.3848243622769</t>
+          <t>8.617367341441684</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-18.95988124871053</t>
+          <t>-24.41489498891521</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,180 +5765,180 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>38.93</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>38.27</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>38.12</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>37.94</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>112.66</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-94.16</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>5139366.403508772</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>1554812.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>1653431.8</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>1218436.9</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>899236.42</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>434994</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>61437.1370011157</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>159341.99</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>38.74</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>38.18</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>38.09</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>37.92</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>119.37</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-95.80</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>5143476.43045388</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>1858205.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1362021.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>1090324.2</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>886390.3</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>271696</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>43636.25436182194</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>171885.78</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>97.804</t>
+          <t>47.361</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,17 +6201,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6221,37 +6221,37 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>122.70</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-97.05</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>1194000.6</t>
+          <t>1362021.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1099173.5</t>
+          <t>1090324.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>862631.28</t>
+          <t>886390.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>271696</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>20318.15867527142</t>
+          <t>43636.25436182194</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>151160.31</v>
+        <v>171885.78</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,22 +6354,22 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>97.804</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-29.39</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,17 +6612,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6652,37 +6652,37 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.48999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>95.43</t>
+          <t>122.70</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-97.96</t>
+          <t>-97.05</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>192853.0</t>
+          <t>3816336.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>632796.4</t>
+          <t>1194000.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>896121.8</t>
+          <t>1099173.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>793956.36</t>
+          <t>862631.28</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-263325</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3471.32313732002</t>
+          <t>20318.15867527142</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-93645.84</v>
+        <v>151160.31</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,37 +6785,37 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,89 +6912,89 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>22.453</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-29.39</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-21.50</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>38.7</t>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,231 +7022,231 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>95.43</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-97.96</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>5139366.403508772</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>192853.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>632796.4</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>896121.8</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>793956.36</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-263325</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-3471.32313732002</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>-93645.84</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>146.80</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-98.45</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>5143476.43045388</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>844953.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>777039.2</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>989800.5</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>846117.6</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-212761</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>12924.04373596508</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>-51794.1</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>-16.62039607625393</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-56.83211958604829</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>-36.50799374924871</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>22.453</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-21.50</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,22 +7489,22 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7514,37 +7514,37 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>125.68</t>
+          <t>146.80</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-99.02</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>97758.0</t>
+          <t>844953.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>783442.0</t>
+          <t>777039.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1004704.0</t>
+          <t>989800.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>862053.28</t>
+          <t>846117.6</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-221262</t>
+          <t>-212761</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>24690.97823852344</t>
+          <t>12924.04373596508</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-60023.96</v>
+        <v>-51794.1</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7647,22 +7647,22 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26.841</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-22.02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,93 +7884,93 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>38.08</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>38.06</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>125.68</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-99.33</t>
+          <t>-99.02</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1018103.0</t>
+          <t>97758.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>818627.4</t>
+          <t>783442.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1079403.2</t>
+          <t>1004704.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>887081.7</t>
+          <t>862053.28</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-260775</t>
+          <t>-221262</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>40093.6937381743</t>
+          <t>24690.97823852344</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>10419.42</v>
+        <v>-60023.96</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,22 +8078,22 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26.611</t>
+          <t>26.841</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,32 +8356,32 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -8391,17 +8391,17 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-99.19</t>
+          <t>-99.33</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1010315.0</t>
+          <t>1018103.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1004346.4</t>
+          <t>818627.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1019567.1</t>
+          <t>1079403.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>890132.52</t>
+          <t>887081.7</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-15220</t>
+          <t>-260775</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>45489.0164861283</t>
+          <t>40093.6937381743</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>12072.3</v>
+        <v>10419.42</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,27 +8509,27 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>37.95</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>38.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,42 +8636,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>26.611</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>24.089</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,275 +8767,275 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>38.01</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>37.82</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-49.94</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-99.19</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>5139366.403508772</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>1010315.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>1004346.4</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>1019567.1</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>890132.52</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-15220</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>45489.0164861283</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>12072.3</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
           <t>38.0</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>9.26</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>45.08%</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>-52.41%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>30.36</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>3941</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>利華-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
         <is>
           <t>38.0</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>37.8</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-99.09</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>5143476.43045388</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>914067.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1159447.2</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>1136493.7</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>890441.62</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>22953</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>51564.78358608099</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>14836.83</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>-16.62039607625393</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-56.83211958604829</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>-36.50799374924871</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="BV20" t="inlineStr">
-        <is>
-          <t>45.08%</t>
-        </is>
-      </c>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>-52.41%</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>30.53</t>
-        </is>
-      </c>
-      <c r="BY20" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="BZ20" t="inlineStr">
-        <is>
-          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA20" t="inlineStr">
-        <is>
-          <t>利華-紡織纖維-上市</t>
-        </is>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
         <is>
           <t>37.95</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23.073</t>
+          <t>24.089</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-41.58</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-98.93</t>
+          <t>-99.09</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>876967.0</t>
+          <t>914067.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1202561.8</t>
+          <t>1159447.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1104605.4</t>
+          <t>1136493.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>893305.56</t>
+          <t>890441.62</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>97956</t>
+          <t>22953</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>58242.59369744026</t>
+          <t>51564.78358608099</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>28568.56</v>
+        <v>14836.83</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
+          <t>37.95</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
           <t>38.2</t>
         </is>
       </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.166</t>
+          <t>23.073</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,47 +9629,47 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9684,24 +9684,24 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-41.58</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-98.82</t>
+          <t>-98.93</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>273685.0</t>
+          <t>876967.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1225966.0</t>
+          <t>1202561.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1062498.1</t>
+          <t>1104605.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>889282.16</t>
+          <t>893305.56</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>163467</t>
+          <t>97956</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>63637.87322180605</t>
+          <t>58242.59369744026</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>51140.01</v>
+        <v>28568.56</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>51.172</t>
+          <t>7.166</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,79 +10060,79 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>38.02</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>37.78</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-13.24</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>37.98999999999999</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>37.99</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>37.77</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-68.95</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-98.78</t>
+          <t>-98.82</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5143476.43045388</t>
+          <t>5139366.403508772</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1946698.0</t>
+          <t>273685.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1340179.0</t>
+          <t>1225966.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1046531.2</t>
+          <t>1062498.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>896654.42</t>
+          <t>889282.16</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>293647</t>
+          <t>163467</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>65910.21280722857</t>
+          <t>63637.87322180605</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>146195.86</v>
+        <v>51140.01</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-16.62039607625393</t>
+          <t>-59.62418527250035</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-56.83211958604829</t>
+          <t>18.25751421608448</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-36.50799374924871</t>
+          <t>-21.80315938182285</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,42 +1009,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,22 +1054,22 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1178368.2</t>
+          <t>1155730.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>758152.44</t>
+          <t>760224.08</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>102422.58</v>
+        <v>30095.87</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,275 +1440,275 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>12.42</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-37.02</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-104.01</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>4336307.83982684</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1361673.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1178368.2</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>876208.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>758152.44</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>302159</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>41662.17113525204</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>102422.58</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>9.72</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>12.4</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-80.76</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-103.64</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>4342197.268786128</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>98400.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>983189.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>768634.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>737617.34</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>214555</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>30614.82493160136</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>74825.17</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>9.76</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>12.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>149.527</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1871,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-134.75</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-103.64</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1173448.8</t>
+          <t>983189.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>813852.9</t>
+          <t>768634.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>742038.84</t>
+          <t>737617.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>22576.57974837472</t>
+          <t>30614.82493160136</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>168078.66</v>
+        <v>74825.17</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>190.257</t>
+          <t>149.527</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,52 +2302,52 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-210.39</t>
+          <t>-134.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.92</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2316222.0</t>
+          <t>1828476.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>919222.4</t>
+          <t>1173448.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>656614.8</t>
+          <t>813852.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>708081.34</t>
+          <t>742038.84</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>262607</t>
+          <t>359595</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3878.344779343355</t>
+          <t>22576.57974837472</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>109929.84</v>
+        <v>168078.66</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.042</t>
+          <t>190.257</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,37 +2753,37 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-427.83</t>
+          <t>-210.39</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-101.92</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>287070.0</t>
+          <t>2316222.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>536609.4</t>
+          <t>919222.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>526455.8</t>
+          <t>656614.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>668527.98</t>
+          <t>708081.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>262607</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-24570.74249267402</t>
+          <t>-3878.344779343355</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-29324.47</v>
+        <v>109929.84</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>23.042</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-7719.21</t>
+          <t>-427.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,205 +3234,205 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-100.91</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>4336307.83982684</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>287070.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>536609.4</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>526455.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>668527.98</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-24570.74249267402</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-29324.47</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-99.94</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>4342197.268786128</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>385780.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>574049.2</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>513642.2</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>677934.64</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>60406</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-23706.4286024678</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-9802.75</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>9.72</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
         <is>
           <t>12.35</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>9.76</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>12.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>86.144</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>12.38</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>12.36</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-553.19</t>
+          <t>-7719.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-98.71</t>
+          <t>-99.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1049696.0</t>
+          <t>385780.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>554078.4</t>
+          <t>574049.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>549015.7</t>
+          <t>513642.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>681025.48</t>
+          <t>677934.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-26234.36937883106</t>
+          <t>-23706.4286024678</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>7859.44</v>
+        <v>-9802.75</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.054</t>
+          <t>86.144</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,47 +4026,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-243.89</t>
+          <t>-553.19</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-96.93</t>
+          <t>-98.71</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>557344.0</t>
+          <t>1049696.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>454257.0</t>
+          <t>554078.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>459605.5</t>
+          <t>549015.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>684653.76</t>
+          <t>681025.48</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-32433.24313132533</t>
+          <t>-26234.36937883106</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-38323.41</v>
+        <v>7859.44</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33.103</t>
+          <t>46.054</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.61</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,47 +4457,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4512,22 +4512,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-130.21</t>
+          <t>-243.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-95.06</t>
+          <t>-96.93</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>403157.0</t>
+          <t>557344.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>394007.2</t>
+          <t>454257.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>461441.1</t>
+          <t>459605.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>674235.88</t>
+          <t>684653.76</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-67433</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-31362.30293904196</t>
+          <t>-32433.24313132533</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-50178.22</v>
+        <v>-38323.41</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>38.499</t>
+          <t>33.103</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.50</t>
+          <t>-130.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-93.45</t>
+          <t>-95.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4342197.268786128</t>
+          <t>4336307.83982684</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>474269.0</t>
+          <t>403157.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>516302.2</t>
+          <t>394007.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>609210.8</t>
+          <t>461441.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>687313.42</t>
+          <t>674235.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-92908</t>
+          <t>-67433</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-27941.22684321377</t>
+          <t>-31362.30293904196</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-48801.55</v>
+        <v>-50178.22</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23.043</t>
+          <t>38.499</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,69 +5203,69 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-15.25</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.24</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-22.13</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,275 +5319,275 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>12.37</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-57.50</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-93.45</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>4336307.83982684</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>474269.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>516302.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>609210.8</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>687313.42</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-92908</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-27941.22684321377</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-48801.55</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>12.59</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-32.41</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-92.51</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>4342197.268786128</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>285926.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>453235.2</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>582058.9</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>679543.52</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-128823</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-24148.44165449194</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-52711.1</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>9.72</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
         <is>
           <t>12.35</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>9.76</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>12.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1653431.8</t>
+          <t>1685554.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>899236.42</t>
+          <t>908619.58</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>159341.99</v>
+        <v>105384.41</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-94.16</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>1362021.0</t>
+          <t>1653431.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1090324.2</t>
+          <t>1218436.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>886390.3</t>
+          <t>899236.42</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>271696</t>
+          <t>434994</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>43636.25436182194</t>
+          <t>61437.1370011157</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>171885.78</v>
+        <v>159341.99</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>97.804</t>
+          <t>47.361</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6652,37 +6652,37 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>122.70</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-97.05</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1194000.6</t>
+          <t>1362021.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1099173.5</t>
+          <t>1090324.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>862631.28</t>
+          <t>886390.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>271696</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>20318.15867527142</t>
+          <t>43636.25436182194</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>151160.31</v>
+        <v>171885.78</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>97.804</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-29.39</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7063,17 +7063,17 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7083,37 +7083,37 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.48999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>95.43</t>
+          <t>122.70</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-97.96</t>
+          <t>-97.05</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>192853.0</t>
+          <t>3816336.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>632796.4</t>
+          <t>1194000.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>896121.8</t>
+          <t>1099173.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>793956.36</t>
+          <t>862631.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-263325</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3471.32313732002</t>
+          <t>20318.15867527142</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-93645.84</v>
+        <v>151160.31</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,89 +7343,89 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>22.453</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-29.39</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-21.50</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>38.7</t>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,22 +7453,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -7479,202 +7479,202 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>95.43</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-97.96</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>5134065.650364963</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>192853.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>632796.4</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>896121.8</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>793956.36</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-263325</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-3471.32313732002</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>-93645.84</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>146.80</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-98.45</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>5139366.403508772</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>844953.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>777039.2</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>989800.5</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>846117.6</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>-212761</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>12924.04373596508</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>-51794.1</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BS17" t="inlineStr">
         <is>
           <t>2.02</t>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>22.453</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-21.50</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,22 +7920,22 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -7945,37 +7945,37 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>125.68</t>
+          <t>146.80</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-99.02</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>97758.0</t>
+          <t>844953.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>783442.0</t>
+          <t>777039.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1004704.0</t>
+          <t>989800.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>862053.28</t>
+          <t>846117.6</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-221262</t>
+          <t>-212761</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>24690.97823852344</t>
+          <t>12924.04373596508</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-60023.96</v>
+        <v>-51794.1</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26.841</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8240,17 +8240,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-22.02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -8341,67 +8341,67 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>38.08</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>38.06</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>125.68</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-99.33</t>
+          <t>-99.02</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1018103.0</t>
+          <t>97758.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>818627.4</t>
+          <t>783442.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1079403.2</t>
+          <t>1004704.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>887081.7</t>
+          <t>862053.28</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-260775</t>
+          <t>-221262</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>40093.6937381743</t>
+          <t>24690.97823852344</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>10419.42</v>
+        <v>-60023.96</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26.611</t>
+          <t>26.841</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-24.16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,32 +8787,32 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -8822,17 +8822,17 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-99.19</t>
+          <t>-99.33</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1010315.0</t>
+          <t>1018103.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1004346.4</t>
+          <t>818627.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1019567.1</t>
+          <t>1079403.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>890132.52</t>
+          <t>887081.7</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-15220</t>
+          <t>-260775</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>45489.0164861283</t>
+          <t>40093.6937381743</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>12072.3</v>
+        <v>10419.42</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>37.95</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>38.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,42 +9067,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>26.611</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>24.089</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,270 +9203,270 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>38.01</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>37.82</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-49.94</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-99.19</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>5134065.650364963</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>1010315.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>1004346.4</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>1019567.1</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>890132.52</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-15220</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>45489.0164861283</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>12072.3</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
           <t>38.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>45.08%</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>-52.41%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>30.03</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>利華-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
         <is>
           <t>38.0</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>37.8</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-99.09</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>5139366.403508772</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>914067.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1159447.2</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>1136493.7</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>890441.62</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>22953</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>51564.78358608099</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>14836.83</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>9.26</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>45.08%</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>-52.41%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>30.36</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>利華-紡織纖維-上市</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
         <is>
           <t>37.95</t>
         </is>
       </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23.073</t>
+          <t>24.089</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,32 +9644,32 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-41.58</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-98.93</t>
+          <t>-99.09</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>876967.0</t>
+          <t>914067.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1202561.8</t>
+          <t>1159447.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1104605.4</t>
+          <t>1136493.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>893305.56</t>
+          <t>890441.62</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>97956</t>
+          <t>22953</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>58242.59369744026</t>
+          <t>51564.78358608099</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>28568.56</v>
+        <v>14836.83</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
+          <t>37.95</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
           <t>38.2</t>
         </is>
       </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.166</t>
+          <t>23.073</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,42 +10065,42 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -10115,24 +10115,24 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-41.58</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-98.82</t>
+          <t>-98.93</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5139366.403508772</t>
+          <t>5134065.650364963</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>273685.0</t>
+          <t>876967.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1225966.0</t>
+          <t>1202561.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1062498.1</t>
+          <t>1104605.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>889282.16</t>
+          <t>893305.56</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>163467</t>
+          <t>97956</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>63637.87322180605</t>
+          <t>58242.59369744026</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>51140.01</v>
+        <v>28568.56</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,57 +1014,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>711615.4</t>
+          <t>586460.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>672637.4</t>
+          <t>682993.62</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>599610</v>
+        <v>735900</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>12.27</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>12.34</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>611373.4</t>
+          <t>711615.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>693766.12</t>
+          <t>672637.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>786663</v>
+        <v>599610</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,57 +1886,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>819736.0</t>
+          <t>611373.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>697643.76</t>
+          <t>693766.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>636249</v>
+        <v>786663</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,52 +2322,52 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2377,220 +2377,220 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>4317358.631276901</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>819736.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>697643.76</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>636249</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>4321975.74137931</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1155730.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>760224.08</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>173882</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>9.65</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>19.07</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
         <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>9.41</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,42 +2758,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2803,22 +2803,22 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1178368.2</t>
+          <t>1155730.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>758152.44</t>
+          <t>760224.08</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>102422.5752553308</t>
+          <t>30095.86714513553</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1361673</v>
+        <v>173882</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,280 +3194,280 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>12.42</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-37.02</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-104.01</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>4317358.631276901</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1361673.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1178368.2</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>876208.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>758152.44</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>302159</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>41662.17113525204</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>102422.5752553308</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1361673</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>9.65</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>19.07</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>12.4</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-80.76</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-103.64</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>4321975.74137931</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>98400.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>983189.6</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>768634.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>737617.34</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>214555</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>30614.82493160136</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>74825.17343934788</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>98400</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>9.41</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>12.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>149.527</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,57 +3630,57 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-134.75</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-103.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1173448.8</t>
+          <t>983189.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>813852.9</t>
+          <t>768634.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>742038.84</t>
+          <t>737617.34</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>22576.57974837472</t>
+          <t>30614.82493160136</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>168078.6646508242</t>
+          <t>74825.17343934788</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1828476</v>
+        <v>98400</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>190.257</t>
+          <t>149.527</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,52 +4066,52 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4121,22 +4121,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-210.39</t>
+          <t>-134.75</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.92</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2316222.0</t>
+          <t>1828476.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>919222.4</t>
+          <t>1173448.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>656614.8</t>
+          <t>813852.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>708081.34</t>
+          <t>742038.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>262607</t>
+          <t>359595</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3878.344779343355</t>
+          <t>22576.57974837472</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>109929.8426439753</t>
+          <t>168078.6646508242</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>2316222</v>
+        <v>1828476</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23.042</t>
+          <t>190.257</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,37 +4522,37 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-427.83</t>
+          <t>-210.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-101.92</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>287070.0</t>
+          <t>2316222.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>536609.4</t>
+          <t>919222.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>526455.8</t>
+          <t>656614.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>668527.98</t>
+          <t>708081.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>262607</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-24570.74249267402</t>
+          <t>-3878.344779343355</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-29324.46888880822</t>
+          <t>109929.8426439753</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>287070</v>
+        <v>2316222</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>23.042</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,42 +4938,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-7719.21</t>
+          <t>-427.83</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,210 +5008,210 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-100.91</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>4317358.631276901</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>287070.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>536609.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>526455.8</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>668527.98</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-24570.74249267402</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-29324.46888880822</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>287070</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-99.94</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>4321975.74137931</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>385780.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>574049.2</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>513642.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>677934.64</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>60406</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-23706.4286024678</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-9802.754332469893</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>385780</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>9.65</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>19.07</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>9.41</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>12.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>86.144</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
+          <t>12.38</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>12.36</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-553.19</t>
+          <t>-7719.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-98.71</t>
+          <t>-99.94</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4321975.74137931</t>
+          <t>4317358.631276901</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1049696.0</t>
+          <t>385780.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>554078.4</t>
+          <t>574049.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>549015.7</t>
+          <t>513642.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>681025.48</t>
+          <t>677934.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-26234.36937883106</t>
+          <t>-23706.4286024678</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>7859.436259887414</t>
+          <t>-9802.754332469893</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1049696</v>
+        <v>385780</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>21.509</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,67 +5815,67 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>842388.0</t>
+          <t>698847.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>880787.42</t>
+          <t>885973.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>356962</v>
+        <v>837110</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,275 +6251,275 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>38.21</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-88.95</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>5109677.760522496</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>356962.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>842388.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>1102204.5</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>880787.42</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-259816</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>33397.9977080884</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-58565.17029805912</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>356962</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>45.08%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>-52.41%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>利華-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
         <is>
           <t>38.2</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-89.57</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>5115279.523255814</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>1003538.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1142636.6</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>1168318.6</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>889614.54</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-25682</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>50118.57370920612</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-1252.468849041965</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>1003538</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>9.09</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>45.08%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>-52.41%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>30.13</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>3866</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>利華-紡織纖維-上市</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,72 +6687,72 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1705196.2</t>
+          <t>1142636.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1168996.3</t>
+          <t>1168318.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>888941.14</t>
+          <t>889614.54</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>-25682</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>59458.76326525123</t>
+          <t>50118.57370920612</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>11391.54996559117</t>
+          <t>-1252.468849041965</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>291061</v>
+        <v>1003538</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,72 +7123,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1685554.6</t>
+          <t>1705196.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>908619.58</t>
+          <t>888941.14</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>1005567</v>
+        <v>291061</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1653431.8</t>
+          <t>1685554.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>899236.42</t>
+          <t>908619.58</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>159341.9915172313</t>
+          <t>105384.4143448677</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1554812</v>
+        <v>1005567</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-94.16</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1362021.0</t>
+          <t>1653431.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1090324.2</t>
+          <t>1218436.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>886390.3</t>
+          <t>899236.42</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>271696</t>
+          <t>434994</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>43636.25436182194</t>
+          <t>61437.1370011157</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>171885.7806378498</t>
+          <t>159341.9915172313</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1858205</v>
+        <v>1554812</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>97.804</t>
+          <t>47.361</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,17 +8446,17 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -8466,37 +8466,37 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>122.70</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-97.05</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1194000.6</t>
+          <t>1362021.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1099173.5</t>
+          <t>1090324.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>862631.28</t>
+          <t>886390.3</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>271696</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>20318.15867527142</t>
+          <t>43636.25436182194</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>151160.3086445243</t>
+          <t>171885.7806378498</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>3816336</v>
+        <v>1858205</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>97.804</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-29.39</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8882,17 +8882,17 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8902,37 +8902,37 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.48999999999999</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>95.43</t>
+          <t>122.70</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-97.96</t>
+          <t>-97.05</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>192853.0</t>
+          <t>3816336.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>632796.4</t>
+          <t>1194000.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>896121.8</t>
+          <t>1099173.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>793956.36</t>
+          <t>862631.28</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-263325</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3471.32313732002</t>
+          <t>20318.15867527142</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-93645.84094038804</t>
+          <t>151160.3086445243</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>192853</v>
+        <v>3816336</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,89 +9167,89 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>22.453</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-29.39</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-21.50</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>38.7</t>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,22 +9277,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -9303,207 +9303,207 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>95.43</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-97.96</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>5109677.760522496</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>192853.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>632796.4</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>896121.8</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>793956.36</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-263325</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-3471.32313732002</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-93645.84094038804</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>192853</v>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>146.80</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-98.45</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>5115279.523255814</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>844953.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>777039.2</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>989800.5</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>846117.6</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-212761</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>12924.04373596508</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>-51794.09602810594</t>
-        </is>
-      </c>
-      <c r="BD21" t="n">
-        <v>844953</v>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BT21" t="inlineStr">
         <is>
           <t>2.06</t>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>22.453</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-21.50</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,22 +9749,22 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9774,37 +9774,37 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>125.68</t>
+          <t>146.80</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-99.02</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>97758.0</t>
+          <t>844953.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>783442.0</t>
+          <t>777039.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1004704.0</t>
+          <t>989800.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>862053.28</t>
+          <t>846117.6</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-221262</t>
+          <t>-212761</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>24690.97823852344</t>
+          <t>12924.04373596508</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-60023.95700955624</t>
+          <t>-51794.09602810594</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>97758</v>
+        <v>844953</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26.841</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-24.16</t>
+          <t>-22.02</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,22 +10149,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -10175,67 +10175,67 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>38.08</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>38.06</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>125.68</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-99.33</t>
+          <t>-99.02</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,50 +10260,50 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5115279.523255814</t>
+          <t>5109677.760522496</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1018103.0</t>
+          <t>97758.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>818627.4</t>
+          <t>783442.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1079403.2</t>
+          <t>1004704.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>887081.7</t>
+          <t>862053.28</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-260775</t>
+          <t>-221262</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>40093.6937381743</t>
+          <t>24690.97823852344</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>10419.41862442729</t>
+          <t>-60023.95700955624</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>1018103</v>
+        <v>97758</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,47 +1019,47 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>586460.8</t>
+          <t>581864.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>682993.62</t>
+          <t>673751.64</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>735900</v>
+        <v>150900</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,52 +1455,52 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>711615.4</t>
+          <t>586460.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>672637.4</t>
+          <t>682993.62</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>599610</v>
+        <v>735900</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>12.27</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>12.34</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>611373.4</t>
+          <t>711615.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>693766.12</t>
+          <t>672637.4</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>786663</v>
+        <v>599610</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,52 +2327,52 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>819736.0</t>
+          <t>611373.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>697643.76</t>
+          <t>693766.12</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>636249</v>
+        <v>786663</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,270 +2763,270 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>12.32</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>12.39</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>12.43</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>4311497.58739255</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>819736.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>697643.76</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>636249</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>12.29</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>12.43</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>9.88</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>19.18</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
         <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>4317358.631276901</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1155730.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>760224.08</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>173882</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>9.65</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>19.07</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,37 +3199,37 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3239,22 +3239,22 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1178368.2</t>
+          <t>1155730.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>758152.44</t>
+          <t>760224.08</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>102422.5752553308</t>
+          <t>30095.86714513553</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1361673</v>
+        <v>173882</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,275 +3635,275 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>12.42</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-37.02</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-104.01</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>4311497.58739255</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>1361673.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1178368.2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>876208.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>758152.44</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>302159</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>41662.17113525204</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>102422.5752553308</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>1361673</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>9.88</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>19.18</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>12.4</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-80.76</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-103.64</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>4317358.631276901</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>98400.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>983189.6</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>768634.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>737617.34</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>214555</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>30614.82493160136</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>74825.17343934788</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>98400</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>9.65</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>19.07</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>12.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>149.527</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,52 +4071,52 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-134.75</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-103.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1173448.8</t>
+          <t>983189.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>813852.9</t>
+          <t>768634.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>742038.84</t>
+          <t>737617.34</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>22576.57974837472</t>
+          <t>30614.82493160136</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>168078.6646508242</t>
+          <t>74825.17343934788</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1828476</v>
+        <v>98400</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>190.257</t>
+          <t>149.527</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,47 +4507,47 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4557,22 +4557,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-210.39</t>
+          <t>-134.75</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.92</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2316222.0</t>
+          <t>1828476.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>919222.4</t>
+          <t>1173448.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>656614.8</t>
+          <t>813852.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>708081.34</t>
+          <t>742038.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>262607</t>
+          <t>359595</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3878.344779343355</t>
+          <t>22576.57974837472</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>109929.8426439753</t>
+          <t>168078.6646508242</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2316222</v>
+        <v>1828476</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23.042</t>
+          <t>190.257</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4958,37 +4958,37 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4998,17 +4998,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-427.83</t>
+          <t>-210.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-101.92</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4317358.631276901</t>
+          <t>4311497.58739255</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>287070.0</t>
+          <t>2316222.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>536609.4</t>
+          <t>919222.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>526455.8</t>
+          <t>656614.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>668527.98</t>
+          <t>708081.34</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>262607</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-24570.74249267402</t>
+          <t>-3878.344779343355</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-29324.46888880822</t>
+          <t>109929.8426439753</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>287070</v>
+        <v>2316222</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>23.042</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,37 +5379,37 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7719.21</t>
+          <t>-427.83</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5444,210 +5444,210 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-100.91</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>4311497.58739255</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>287070.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>536609.4</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>526455.8</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>668527.98</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-24570.74249267402</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-29324.46888880822</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>287070</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-99.94</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>4317358.631276901</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>385780.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>574049.2</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>513642.2</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>677934.64</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>60406</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-23706.4286024678</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-9802.754332469893</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>385780</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>9.88</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>19.18</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>9.65</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>19.07</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>12.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,107 +5679,107 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-44.84</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>21.509</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-40.58</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,17 +5815,17 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -5835,27 +5835,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -5865,17 +5865,17 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-88.76</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>698847.6</t>
+          <t>641872.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1176139.7</t>
+          <t>1163713.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>885973.0</t>
+          <t>872957.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-477292</t>
+          <t>-521840</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>18843.10082147177</t>
+          <t>5134.862313037787</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-61208.83205491968</t>
+          <t>-70260.4494833491</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>837110</v>
+        <v>720693</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>21.509</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6210,14 +6210,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,67 +6251,67 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>842388.0</t>
+          <t>698847.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>880787.42</t>
+          <t>885973.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>356962</v>
+        <v>837110</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,275 +6687,275 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>38.21</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-88.95</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>5103839.154347826</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>356962.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>842388.0</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>1102204.5</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>880787.42</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-259816</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>33397.9977080884</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-58565.17029805912</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>356962</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>45.08%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>-52.41%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>30.26</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>3851</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>利華-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
         <is>
           <t>38.2</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-89.57</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>5109677.760522496</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>1003538.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1142636.6</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>1168318.6</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>889614.54</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-25682</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>50118.57370920612</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-1252.468849041965</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>1003538</v>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>45.08%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>-52.41%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>3871</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>利華-紡織纖維-上市</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,72 +7123,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1705196.2</t>
+          <t>1142636.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1168996.3</t>
+          <t>1168318.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>888941.14</t>
+          <t>889614.54</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>-25682</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>59458.76326525123</t>
+          <t>50118.57370920612</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>11391.54996559117</t>
+          <t>-1252.468849041965</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>291061</v>
+        <v>1003538</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,72 +7559,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1685554.6</t>
+          <t>1705196.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>908619.58</t>
+          <t>888941.14</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1005567</v>
+        <v>291061</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7752,17 +7752,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1653431.8</t>
+          <t>1685554.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>899236.42</t>
+          <t>908619.58</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>159341.9915172313</t>
+          <t>105384.4143448677</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1554812</v>
+        <v>1005567</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-94.16</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1362021.0</t>
+          <t>1653431.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1090324.2</t>
+          <t>1218436.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>886390.3</t>
+          <t>899236.42</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>271696</t>
+          <t>434994</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43636.25436182194</t>
+          <t>61437.1370011157</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>171885.7806378498</t>
+          <t>159341.9915172313</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>1858205</v>
+        <v>1554812</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>97.804</t>
+          <t>47.361</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,17 +8882,17 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8902,37 +8902,37 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>122.70</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-97.05</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1194000.6</t>
+          <t>1362021.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1099173.5</t>
+          <t>1090324.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>862631.28</t>
+          <t>886390.3</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>271696</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>20318.15867527142</t>
+          <t>43636.25436182194</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>151160.3086445243</t>
+          <t>171885.7806378498</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>3816336</v>
+        <v>1858205</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>97.804</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-29.39</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9338,37 +9338,37 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.48999999999999</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>95.43</t>
+          <t>122.70</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-97.96</t>
+          <t>-97.05</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>192853.0</t>
+          <t>3816336.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>632796.4</t>
+          <t>1194000.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>896121.8</t>
+          <t>1099173.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>793956.36</t>
+          <t>862631.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-263325</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3471.32313732002</t>
+          <t>20318.15867527142</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-93645.84094038804</t>
+          <t>151160.3086445243</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>192853</v>
+        <v>3816336</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,89 +9603,89 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>22.453</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-29.39</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-21.50</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>38.7</t>
@@ -9698,12 +9698,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,22 +9713,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -9739,210 +9739,210 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>95.43</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-97.96</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>5103839.154347826</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>192853.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>632796.4</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>896121.8</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>793956.36</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-263325</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-3471.32313732002</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-93645.84094038804</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>192853</v>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>146.80</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-98.45</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>5109677.760522496</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>844953.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>777039.2</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>989800.5</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>846117.6</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-212761</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>12924.04373596508</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>-51794.09602810594</t>
-        </is>
-      </c>
-      <c r="BD22" t="n">
-        <v>844953</v>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>22.453</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-21.50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,22 +10185,22 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10210,37 +10210,37 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>125.68</t>
+          <t>146.80</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-99.02</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5109677.760522496</t>
+          <t>5103839.154347826</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>97758.0</t>
+          <t>844953.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>783442.0</t>
+          <t>777039.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1004704.0</t>
+          <t>989800.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>862053.28</t>
+          <t>846117.6</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-221262</t>
+          <t>-212761</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>24690.97823852344</t>
+          <t>12924.04373596508</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-60023.95700955624</t>
+          <t>-51794.09602810594</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>97758</v>
+        <v>844953</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.26</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>113.361</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,112 +898,112 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.24</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-33.03</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,132 +1029,132 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>296.53</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-102.95</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4308570.341201717</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1510235.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>756661.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>788198.8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>690434.86</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-31537</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>14058.48181016269</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>26112.93996276357</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>1510235</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-105.13</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>4311497.58739255</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>150900.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>581864.4</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>868797.5</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>673751.64</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-286933</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>11866.76214605344</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-46258.61678213044</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>150900</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
       <c r="BG2" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1369,49 +1369,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1419,27 +1419,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,52 +1450,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>586460.8</t>
+          <t>581864.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>682993.62</t>
+          <t>673751.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>735900</v>
+        <v>150900</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1805,49 +1805,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1855,27 +1855,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,57 +1886,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>711615.4</t>
+          <t>586460.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>672637.4</t>
+          <t>682993.62</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>599610</v>
+        <v>735900</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>11.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2241,49 +2241,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>12.27</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>12.34</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>611373.4</t>
+          <t>711615.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>693766.12</t>
+          <t>672637.4</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>786663</v>
+        <v>599610</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,27 +2727,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,57 +2758,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>819736.0</t>
+          <t>611373.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>697643.76</t>
+          <t>693766.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>636249</v>
+        <v>786663</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3113,49 +3113,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,52 +3194,52 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3249,220 +3249,220 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>4308570.341201717</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>819736.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>697643.76</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>636249</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>4311497.58739255</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1155730.6</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>760224.08</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>173882</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>10.63</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>19.49</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
         <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>1176</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3549,49 +3549,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3599,27 +3599,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,42 +3630,42 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3675,22 +3675,22 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1178368.2</t>
+          <t>1155730.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>758152.44</t>
+          <t>760224.08</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>102422.5752553308</t>
+          <t>30095.86714513553</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1361673</v>
+        <v>173882</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3985,49 +3985,49 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4035,27 +4035,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,282 +4066,282 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>12.42</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-37.02</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-104.01</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>4308570.341201717</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1361673.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1178368.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>876208.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>758152.44</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>302159</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>41662.17113525204</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>102422.5752553308</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>1361673</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>10.63</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>19.49</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-80.76</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-103.64</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>4311497.58739255</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>98400.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>983189.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>768634.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>737617.34</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>214555</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>30614.82493160136</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>74825.17343934788</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>98400</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>1176</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
       <c r="CH9" t="inlineStr">
         <is>
           <t>16.36</t>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>149.527</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,49 +4421,49 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4471,27 +4471,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,57 +4502,57 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-134.75</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-103.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1173448.8</t>
+          <t>983189.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>813852.9</t>
+          <t>768634.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>742038.84</t>
+          <t>737617.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>22576.57974837472</t>
+          <t>30614.82493160136</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>168078.6646508242</t>
+          <t>74825.17343934788</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1828476</v>
+        <v>98400</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>190.257</t>
+          <t>149.527</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,49 +4857,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4907,27 +4907,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,52 +4938,52 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4993,22 +4993,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-210.39</t>
+          <t>-134.75</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.92</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2316222.0</t>
+          <t>1828476.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>919222.4</t>
+          <t>1173448.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>656614.8</t>
+          <t>813852.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>708081.34</t>
+          <t>742038.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>262607</t>
+          <t>359595</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3878.344779343355</t>
+          <t>22576.57974837472</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>109929.8426439753</t>
+          <t>168078.6646508242</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2316222</v>
+        <v>1828476</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23.042</t>
+          <t>190.257</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,49 +5293,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-10-22 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>12.8</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5343,27 +5343,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-23.81</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,37 +5394,37 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5434,17 +5434,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-427.83</t>
+          <t>-210.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-101.92</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4311497.58739255</t>
+          <t>4308570.341201717</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>287070.0</t>
+          <t>2316222.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>536609.4</t>
+          <t>919222.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>526455.8</t>
+          <t>656614.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>668527.98</t>
+          <t>708081.34</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>262607</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-24570.74249267402</t>
+          <t>-3878.344779343355</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-29324.46888880822</t>
+          <t>109929.8426439753</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>287070</v>
+        <v>2316222</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18.707</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,72 +5694,72 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-45.70</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>38.65</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-44.84</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5774,32 +5774,32 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>0.13</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>0.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,225 +5810,225 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38.23</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-88.98</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>5097016.165701881</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>635547.8</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>1170372.0</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>848534.38</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-534824</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-12491.16964991662</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-109434.3454461659</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>259436</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-88.76</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>5103839.154347826</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>641872.8</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>1163713.7</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>872957.0</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-521840</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>5134.862313037787</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-70260.4494833491</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>720693</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,107 +6115,107 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-44.84</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>21.509</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-40.58</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,22 +6246,22 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -6271,27 +6271,27 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -6301,17 +6301,17 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-88.76</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>698847.6</t>
+          <t>641872.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1176139.7</t>
+          <t>1163713.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>885973.0</t>
+          <t>872957.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-477292</t>
+          <t>-521840</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>18843.10082147177</t>
+          <t>5134.862313037787</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-61208.83205491968</t>
+          <t>-70260.4494833491</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>837110</v>
+        <v>720693</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>21.509</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6646,14 +6646,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,72 +6682,72 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>842388.0</t>
+          <t>698847.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>880787.42</t>
+          <t>885973.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>356962</v>
+        <v>837110</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,280 +7118,280 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>38.21</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-88.95</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>5097016.165701881</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>356962.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>842388.0</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>1102204.5</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>880787.42</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-259816</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>33397.9977080884</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-58565.17029805912</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>356962</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>45.08%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>-52.41%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>利華-紡織纖維-上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
         <is>
           <t>38.2</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-89.57</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>5103839.154347826</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>1003538.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1142636.6</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>1168318.6</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>889614.54</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-25682</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>50118.57370920612</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-1252.468849041965</t>
-        </is>
-      </c>
-      <c r="BD16" t="n">
-        <v>1003538</v>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>9.05</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>45.08%</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>-52.41%</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>30.26</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>3851</t>
-        </is>
-      </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>毛條63.77%、防縮毛條35.73%、代工及脂肪酸0.50% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>利華-紡織纖維-上市</t>
-        </is>
-      </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1705196.2</t>
+          <t>1142636.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1168996.3</t>
+          <t>1168318.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>888941.14</t>
+          <t>889614.54</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>-25682</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>59458.76326525123</t>
+          <t>50118.57370920612</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>11391.54996559117</t>
+          <t>-1252.468849041965</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>291061</v>
+        <v>1003538</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1685554.6</t>
+          <t>1705196.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>908619.58</t>
+          <t>888941.14</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1005567</v>
+        <v>291061</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8188,17 +8188,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1653431.8</t>
+          <t>1685554.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>899236.42</t>
+          <t>908619.58</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>159341.9915172313</t>
+          <t>105384.4143448677</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>1554812</v>
+        <v>1005567</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,12 +8619,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-94.16</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1362021.0</t>
+          <t>1653431.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1090324.2</t>
+          <t>1218436.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>886390.3</t>
+          <t>899236.42</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>271696</t>
+          <t>434994</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43636.25436182194</t>
+          <t>61437.1370011157</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>171885.7806378498</t>
+          <t>159341.9915172313</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1858205</v>
+        <v>1554812</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>97.804</t>
+          <t>47.361</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9338,37 +9338,37 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>122.70</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-97.05</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1194000.6</t>
+          <t>1362021.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1099173.5</t>
+          <t>1090324.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>862631.28</t>
+          <t>886390.3</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>271696</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>20318.15867527142</t>
+          <t>43636.25436182194</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>151160.3086445243</t>
+          <t>171885.7806378498</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>3816336</v>
+        <v>1858205</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>97.804</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,84 +9628,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>8.63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-29.39</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,17 +9734,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9754,17 +9754,17 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9774,37 +9774,37 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.48999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>95.43</t>
+          <t>122.70</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-97.96</t>
+          <t>-97.05</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5103839.154347826</t>
+          <t>5097016.165701881</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>192853.0</t>
+          <t>3816336.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>632796.4</t>
+          <t>1194000.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>896121.8</t>
+          <t>1099173.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>793956.36</t>
+          <t>862631.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-263325</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3471.32313732002</t>
+          <t>20318.15867527142</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-93645.84094038804</t>
+          <t>151160.3086445243</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>192853</v>
+        <v>3816336</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,89 +10039,89 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>22.453</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-29.39</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-21.50</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>38.7</t>
@@ -10134,251 +10134,251 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>4.32</t>
-        </is>
-      </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>95.43</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-97.96</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>5097016.165701881</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>192853.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>632796.4</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>896121.8</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>793956.36</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-263325</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-3471.32313732002</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-93645.84094038804</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>192853</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>146.80</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-98.45</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>5103839.154347826</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>844953.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>777039.2</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>989800.5</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>846117.6</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-212761</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>12924.04373596508</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-51794.09602810594</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>844953</v>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>12.51</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12.42</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1510235.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>756661.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>756661.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>788198.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>690434.86</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>690434.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>26112.93996276357</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1510235</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1510235.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>12.28</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>12.4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>150900.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>581864.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>581864.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>868797.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>673751.64</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>673751.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-46258.61678213044</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>150900</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>150900.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>12.24</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>12.33</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>735900.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>586460.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>586460.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>882414.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>682993.62</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>682993.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-2351.425818331423</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>735900</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>735900.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>12.27</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12.41</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>599610.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>711615.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>711615.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>847402.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>672637.4</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>672637.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-2221.459233678179</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>599610</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>599610.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>12.34</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>786663.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>611373.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>611373.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>892411.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>693766.12</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>693766.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>12646.0451456008</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>786663</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>786663.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>12.32</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>12.39</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>12.43</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.43</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>636249.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>819736.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>819736</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>869479.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>697643.76</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>697643.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>13392.29978937062</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>636249</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>12.29</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>12.43</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>173882.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1155730.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1155730.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>846170.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>760224.08</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>760224.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>30095.86714513553</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>173882</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>173882.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>12.29</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1361673.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1178368.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1178368.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>876208.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>758152.44</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>758152.4399999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>102422.5752553308</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1361673</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1361673.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>12.3</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>12.44</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12.4</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>98400.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>983189.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>983189.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>768634.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>737617.34</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>737617.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>74825.17343934788</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>98400</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>98400.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>12.28</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>12.47</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>12.39</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>12.39</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1828476.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1173448.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1173448.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>813852.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>742038.84</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>742038.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>168078.6646508242</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1828476</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1828476.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>12.26</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>12.39</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12.39</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>2316222.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>919222.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>919222.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>656614.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>708081.34</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>708081.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>109929.8426439753</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>2316222</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2316222.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>38.82</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>38.61</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>38.24</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>38.24</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>259436.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>635547.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>635547.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1170372.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>848534.38</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>848534.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-109434.3454461659</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>259436</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>38.9</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>38.57</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>38.23</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>720693.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>641872.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>641872.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1163713.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>872957.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>872957</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-70260.4494833491</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>720693</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>720693.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>39.1</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>38.23</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>38.23</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>837110.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>698847.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>698847.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1176139.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>885973.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>885973</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-61208.83205491968</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>837110</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>837110.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>39.23999999999999</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>38.21</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>38.21</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>356962.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>842388.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>842388</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1102204.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>880787.42</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>880787.42</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-58565.17029805912</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>356962</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>356962.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>39.32000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38.2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1003538.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1142636.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1142636.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1168318.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>889614.54</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>889614.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1252.468849041965</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1003538</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1003538.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>39.33</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>38.42</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>38.18</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38.18</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>291061.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1705196.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1705196.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1168996.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>888941.14</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>888941.14</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>11391.54996559117</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>291061</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>291061.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>39.14</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>38.36</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>38.15</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>38.15</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1005567.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1685554.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1685554.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1231296.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>908619.58</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>908619.58</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>105384.4143448677</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1005567</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1005567.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>38.93</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>38.27</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>38.12</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>38.12</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1554812.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1653431.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1653431.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1218436.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>899236.42</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>899236.42</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>159341.9915172313</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1554812</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1554812.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>38.74</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>38.18</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>38.09</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>38.09</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1858205.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1362021.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1362021</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1090324.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>886390.3</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>886390.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>171885.7806378498</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1858205</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1858205.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>38.48999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>38.07</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>38.07</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>3816336.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1194000.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1194000.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1099173.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>862631.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>862631.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>151160.3086445243</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>3816336</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>3816336.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>38.3</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>38.09</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>38.05</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>38.05</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>192853.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>632796.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>632796.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>896121.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>793956.36</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>793956.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-93645.84094038804</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>192853</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>192853.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -883,127 +883,127 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30.294</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>113.361</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.92</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>12.38</v>
+        <v>12.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>4653.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.95</t>
+          <t>-99.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>756661.6</v>
+        <v>680506.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>788198.8</t>
+          <t>645939.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>690434.86</v>
+        <v>682702.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-31537</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>14058.48181016269</t>
+          <t>10863.96248323309</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>26112.93996276357</t>
+          <t>-6705.893814879702</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>113.361</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,87 +1328,87 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>7.04</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-33.03</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,126 +1459,126 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>12.32</v>
+        <v>12.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>296.53</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-102.95</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>4303284.998571428</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1510235.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>756661.6</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>788198.8</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>690434.86</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-31537</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>14058.48181016269</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>26112.93996276357</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1510235.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-105.13</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>4308570.341201717</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>150900.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>581864.4</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>868797.5</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>673751.64</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-286933</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>11866.76214605344</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-46258.61678213044</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>150900.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,51 +1874,51 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="AN4" t="n">
         <v>12.4</v>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>586460.8</v>
+        <v>581864.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>682993.62</v>
+        <v>673751.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11.48</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,54 +2304,54 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>711615.4</v>
+        <v>586460.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>672637.4</v>
+        <v>682993.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>611373.4</v>
+        <v>711615.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>693766.12</v>
+        <v>672637.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>819736</v>
+        <v>611373.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>697643.76</v>
+        <v>693766.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,269 +3594,269 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="AN8" t="n">
         <v>12.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>4303284.998571428</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>819736</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>697643.76</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>4308570.341201717</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>1155730.6</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>760224.08</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>19.72</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>10.63</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>19.49</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,42 +4024,42 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4068,19 +4068,19 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1178368.2</v>
+        <v>1155730.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>758152.4399999999</v>
+        <v>760224.08</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>102422.5752553308</t>
+          <t>30095.86714513553</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>12.44</v>
+        <v>12.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-80.76</t>
+          <t>-37.02</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.64</t>
+          <t>-104.01</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>98400.0</t>
+          <t>1361673.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>983189.6</v>
+        <v>1178368.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>768634.0</t>
+          <t>876208.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>737617.34</v>
+        <v>758152.4399999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>214555</t>
+          <t>302159</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>30614.82493160136</t>
+          <t>41662.17113525204</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>74825.17343934788</t>
+          <t>102422.5752553308</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>98400.0</t>
+          <t>1361673.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>149.527</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>12.47</v>
+        <v>12.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-134.75</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-103.64</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1173448.8</v>
+        <v>983189.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>813852.9</t>
+          <t>768634.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>742038.84</v>
+        <v>737617.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>22576.57974837472</t>
+          <t>30614.82493160136</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>168078.6646508242</t>
+          <t>74825.17343934788</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>190.257</t>
+          <t>149.527</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="AN12" t="n">
         <v>12.39</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-210.39</t>
+          <t>-134.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.92</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4308570.341201717</t>
+          <t>4303284.998571428</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2316222.0</t>
+          <t>1828476.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>919222.4</v>
+        <v>1173448.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>656614.8</t>
+          <t>813852.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>708081.34</v>
+        <v>742038.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>262607</t>
+          <t>359595</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3878.344779343355</t>
+          <t>22576.57974837472</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>109929.8426439753</t>
+          <t>168078.6646508242</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2316222.0</t>
+          <t>1828476.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>24.017</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-45.70</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.61</v>
+        <v>38.65</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.24</v>
+        <v>38.25</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-89.40</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>635547.8</v>
+        <v>619199.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1170372.0</t>
+          <t>880917.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>848534.38</v>
+        <v>853954.26</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-534824</t>
+          <t>-261718</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-12491.16964991662</t>
+          <t>-23560.72647054229</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-109434.3454461659</t>
+          <t>-84443.28898398345</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18.707</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,72 +6058,72 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-45.70</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>38.65</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-44.84</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6138,32 +6138,32 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>0.13</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>0.39</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,219 +6174,219 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.57</v>
+        <v>38.61</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.23</v>
+        <v>38.24</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-88.98</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>5091648.645953758</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>635547.8</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>1170372.0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>848534.38</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-534824</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-12491.16964991662</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-109434.3454461659</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-88.76</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>5097016.165701881</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>641872.8</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>1163713.7</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>872957</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-521840</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>5134.862313037787</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-70260.4494833491</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,42 +6473,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>21.509</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-40.58</t>
+          <t>-44.84</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,22 +6604,22 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -6629,43 +6629,43 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.54</v>
+        <v>38.57</v>
       </c>
       <c r="AN15" t="n">
         <v>38.23</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-88.76</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>698847.6</v>
+        <v>641872.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1176139.7</t>
+          <t>1163713.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>885973</v>
+        <v>872957</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-477292</t>
+          <t>-521840</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>18843.10082147177</t>
+          <t>5134.862313037787</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-61208.83205491968</t>
+          <t>-70260.4494833491</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,34 +6903,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21.509</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>-0.39</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>9.315</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6998,14 +6998,14 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,68 +7034,68 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.5</v>
+        <v>38.54</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.21</v>
+        <v>38.23</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>842388</v>
+        <v>698847.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>880787.42</v>
+        <v>885973</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,83 +7464,83 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-89.57</t>
+          <t>-88.95</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>1142636.6</v>
+        <v>842388</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1168318.6</t>
+          <t>1102204.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>889614.54</v>
+        <v>880787.42</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-25682</t>
+          <t>-259816</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>50118.57370920612</t>
+          <t>33397.9977080884</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1252.468849041965</t>
+          <t>-58565.17029805912</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>38.42</v>
+        <v>38.46</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.18</v>
+        <v>38.2</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>1705196.2</v>
+        <v>1142636.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1168996.3</t>
+          <t>1168318.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>888941.14</v>
+        <v>889614.54</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>-25682</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>59458.76326525123</t>
+          <t>50118.57370920612</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>11391.54996559117</t>
+          <t>-1252.468849041965</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>38.36</v>
+        <v>38.42</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.15</v>
+        <v>38.18</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>1685554.6</v>
+        <v>1705196.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>908619.58</v>
+        <v>888941.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>38.27</v>
+        <v>38.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.12</v>
+        <v>38.15</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1653431.8</v>
+        <v>1685554.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>899236.42</v>
+        <v>908619.58</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>159341.9915172313</t>
+          <t>105384.4143448677</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>38.18</v>
+        <v>38.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>38.09</v>
+        <v>38.12</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-94.16</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1362021</v>
+        <v>1653431.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1090324.2</t>
+          <t>1218436.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>886390.3</v>
+        <v>899236.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>271696</t>
+          <t>434994</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>43636.25436182194</t>
+          <t>61437.1370011157</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>171885.7806378498</t>
+          <t>159341.9915172313</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>97.804</t>
+          <t>47.361</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9654,33 +9654,33 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>38.13</v>
+        <v>38.18</v>
       </c>
       <c r="AN22" t="n">
-        <v>38.07</v>
+        <v>38.09</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>122.70</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-97.05</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1194000.6</v>
+        <v>1362021</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1099173.5</t>
+          <t>1090324.2</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>862631.28</v>
+        <v>886390.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>271696</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>20318.15867527142</t>
+          <t>43636.25436182194</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>151160.3086445243</t>
+          <t>171885.7806378498</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,34 +9913,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>97.804</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>-0.78</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>38.3</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.39</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,17 +10044,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10084,33 +10084,33 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.48999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>38.09</v>
+        <v>38.13</v>
       </c>
       <c r="AN23" t="n">
-        <v>38.05</v>
+        <v>38.07</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>95.43</t>
+          <t>122.70</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-97.96</t>
+          <t>-97.05</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5097016.165701881</t>
+          <t>5091648.645953758</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>192853.0</t>
+          <t>3816336.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>632796.4</v>
+        <v>1194000.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>896121.8</t>
+          <t>1099173.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>793956.36</v>
+        <v>862631.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-263325</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3471.32313732002</t>
+          <t>20318.15867527142</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-93645.84094038804</t>
+          <t>151160.3086445243</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>192853.0</t>
+          <t>3816336.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30.294</t>
+          <t>22.251</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.44</v>
+        <v>12.47</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4653.53</t>
+          <t>372.73</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.72</t>
+          <t>-95.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>680506.4</v>
+        <v>620316</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>645939.9</t>
+          <t>665965.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>682702.16</v>
+        <v>675357.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>-45649</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>10863.96248323309</t>
+          <t>3415.10592983446</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-6705.893814879702</t>
+          <t>-37553.60511385801</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,127 +1313,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30.294</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>113.361</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.92</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>12.38</v>
+        <v>12.42</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>4653.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.95</t>
+          <t>-99.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>756661.6</v>
+        <v>680506.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>788198.8</t>
+          <t>645939.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>690434.86</v>
+        <v>682702.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-31537</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>14058.48181016269</t>
+          <t>10863.96248323309</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>26112.93996276357</t>
+          <t>-6705.893814879702</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>113.361</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,87 +1758,87 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>6.69</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-33.03</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,126 +1889,126 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>12.32</v>
+        <v>12.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>296.53</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-102.95</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>4297785.286733238</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1510235.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>756661.6</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>788198.8</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>690434.86</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-31537</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>14058.48181016269</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>26112.93996276357</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1510235.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-105.13</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>4303284.998571428</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>150900.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>581864.4</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>868797.5</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>673751.64</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-286933</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>11866.76214605344</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-46258.61678213044</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>150900.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,51 +2304,51 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="AN5" t="n">
         <v>12.4</v>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>586460.8</v>
+        <v>581864.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>682993.62</v>
+        <v>673751.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,54 +2734,54 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>711615.4</v>
+        <v>586460.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>672637.4</v>
+        <v>682993.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>11.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>611373.4</v>
+        <v>711615.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>693766.12</v>
+        <v>672637.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>819736</v>
+        <v>611373.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>697643.76</v>
+        <v>693766.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,269 +4024,269 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="AN9" t="n">
         <v>12.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>4297785.286733238</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>819736</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>697643.76</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>4303284.998571428</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>1155730.6</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>760224.08</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>10.63</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>19.82</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
         <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>10.59</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>19.72</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,42 +4454,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4498,19 +4498,19 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1178368.2</v>
+        <v>1155730.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>758152.4399999999</v>
+        <v>760224.08</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>102422.5752553308</t>
+          <t>30095.86714513553</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>12.44</v>
+        <v>12.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-80.76</t>
+          <t>-37.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.64</t>
+          <t>-104.01</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>98400.0</t>
+          <t>1361673.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>983189.6</v>
+        <v>1178368.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>768634.0</t>
+          <t>876208.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>737617.34</v>
+        <v>758152.4399999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>214555</t>
+          <t>302159</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>30614.82493160136</t>
+          <t>41662.17113525204</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>74825.17343934788</t>
+          <t>102422.5752553308</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>98400.0</t>
+          <t>1361673.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>149.527</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,54 +5314,54 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>12.47</v>
+        <v>12.44</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-134.75</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-103.64</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4303284.998571428</t>
+          <t>4297785.286733238</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1173448.8</v>
+        <v>983189.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>813852.9</t>
+          <t>768634.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>742038.84</v>
+        <v>737617.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>359595</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>22576.57974837472</t>
+          <t>30614.82493160136</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>168078.6646508242</t>
+          <t>74825.17343934788</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1828476.0</t>
+          <t>98400.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.017</t>
+          <t>1.723</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,79 +5628,79 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-20.05</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>38.7</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-29.71</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>37.85</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,17 +5744,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5784,179 +5784,179 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.65</v>
+        <v>38.68</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.25</v>
+        <v>38.27</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-24.69</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-90.01</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>5084444.435064935</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>561024.2</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>701706.1</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>840829.2</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-140681</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-39784.70197289828</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-129016.5672358562</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-89.40</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>5091648.645953758</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>619199.2</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>880917.9</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>853954.26</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-261718</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-23560.72647054229</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-84443.28898398345</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>24.017</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-45.70</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.61</v>
+        <v>38.65</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.24</v>
+        <v>38.25</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-89.40</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>635547.8</v>
+        <v>619199.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1170372.0</t>
+          <t>880917.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>848534.38</v>
+        <v>853954.26</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-534824</t>
+          <t>-261718</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-12491.16964991662</t>
+          <t>-23560.72647054229</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-109434.3454461659</t>
+          <t>-84443.28898398345</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18.707</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,112 +6488,112 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-45.70</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>38.65</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>0.13</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-44.84</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>0.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,219 +6604,219 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.57</v>
+        <v>38.61</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.23</v>
+        <v>38.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-88.98</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>5084444.435064935</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>635547.8</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>1170372.0</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>848534.38</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-534824</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-12491.16964991662</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-109434.3454461659</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-88.76</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>5091648.645953758</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>641872.8</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>1163713.7</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>872957</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-521840</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>5134.862313037787</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-70260.4494833491</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,107 +6903,107 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-44.84</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>21.509</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-40.58</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,22 +7034,22 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -7059,43 +7059,43 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.54</v>
+        <v>38.57</v>
       </c>
       <c r="AN16" t="n">
         <v>38.23</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-88.76</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>698847.6</v>
+        <v>641872.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1176139.7</t>
+          <t>1163713.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>885973</v>
+        <v>872957</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-477292</t>
+          <t>-521840</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>18843.10082147177</t>
+          <t>5134.862313037787</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-61208.83205491968</t>
+          <t>-70260.4494833491</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>21.509</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,14 +7428,14 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,68 +7464,68 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>38.5</v>
+        <v>38.54</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.21</v>
+        <v>38.23</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>842388</v>
+        <v>698847.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>880787.42</v>
+        <v>885973</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,83 +7894,83 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-89.57</t>
+          <t>-88.95</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>1142636.6</v>
+        <v>842388</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1168318.6</t>
+          <t>1102204.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>889614.54</v>
+        <v>880787.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-25682</t>
+          <t>-259816</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>50118.57370920612</t>
+          <t>33397.9977080884</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1252.468849041965</t>
+          <t>-58565.17029805912</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>38.42</v>
+        <v>38.46</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.18</v>
+        <v>38.2</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>1705196.2</v>
+        <v>1142636.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1168996.3</t>
+          <t>1168318.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>888941.14</v>
+        <v>889614.54</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>-25682</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>59458.76326525123</t>
+          <t>50118.57370920612</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>11391.54996559117</t>
+          <t>-1252.468849041965</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>38.36</v>
+        <v>38.42</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.15</v>
+        <v>38.18</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1685554.6</v>
+        <v>1705196.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>908619.58</v>
+        <v>888941.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>38.27</v>
+        <v>38.36</v>
       </c>
       <c r="AN21" t="n">
-        <v>38.12</v>
+        <v>38.15</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1653431.8</v>
+        <v>1685554.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>899236.42</v>
+        <v>908619.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>159341.9915172313</t>
+          <t>105384.4143448677</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>38.18</v>
+        <v>38.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>38.09</v>
+        <v>38.12</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-94.16</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1362021</v>
+        <v>1653431.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1090324.2</t>
+          <t>1218436.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>886390.3</v>
+        <v>899236.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>271696</t>
+          <t>434994</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>43636.25436182194</t>
+          <t>61437.1370011157</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>171885.7806378498</t>
+          <t>159341.9915172313</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>97.804</t>
+          <t>47.361</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10084,33 +10084,33 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.48999999999999</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>38.13</v>
+        <v>38.18</v>
       </c>
       <c r="AN23" t="n">
-        <v>38.07</v>
+        <v>38.09</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>122.70</t>
+          <t>119.37</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-97.05</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5091648.645953758</t>
+          <t>5084444.435064935</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1194000.6</v>
+        <v>1362021</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1099173.5</t>
+          <t>1090324.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>862631.28</v>
+        <v>886390.3</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>271696</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>20318.15867527142</t>
+          <t>43636.25436182194</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>151160.3086445243</t>
+          <t>171885.7806378498</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>3816336.0</t>
+          <t>1858205.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.251</t>
+          <t>28.123</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-3.39</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-6.85</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>12.8</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>94.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>372.73</t>
+          <t>188.02</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.94</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,63 +1100,63 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>620316</v>
+        <v>547969.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>665965.7</t>
+          <t>567215.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>675357.36</v>
+        <v>665566.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-45649</t>
+          <t>-19245</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3415.10592983446</t>
+          <t>-5194.13927403183</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-37553.60511385801</t>
+          <t>-52544.98789529642</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>13.1</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>13.65</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.294</t>
+          <t>22.251</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1444,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.44</v>
+        <v>12.47</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4653.53</t>
+          <t>372.73</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.72</t>
+          <t>-95.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,63 +1530,63 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>680506.4</v>
+        <v>620316</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>645939.9</t>
+          <t>665965.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>682702.16</v>
+        <v>675357.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>-45649</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>10863.96248323309</t>
+          <t>3415.10592983446</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-6705.893814879702</t>
+          <t>-37553.60511385801</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,127 +1743,127 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>30.294</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>113.361</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.92</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>12.38</v>
+        <v>12.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>4653.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.95</t>
+          <t>-99.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,63 +1960,63 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>756661.6</v>
+        <v>680506.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>788198.8</t>
+          <t>645939.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>690434.86</v>
+        <v>682702.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-31537</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>14058.48181016269</t>
+          <t>10863.96248323309</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>26112.93996276357</t>
+          <t>-6705.893814879702</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>113.361</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,87 +2188,87 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>7.04</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-33.03</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>12.32</v>
+        <v>12.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>296.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-102.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,63 +2390,63 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>581864.4</v>
+        <v>756661.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>868797.5</t>
+          <t>788198.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>673751.64</v>
+        <v>690434.86</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-286933</t>
+          <t>-31537</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>11866.76214605344</t>
+          <t>14058.48181016269</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-46258.61678213044</t>
+          <t>26112.93996276357</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,51 +2734,51 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="AN6" t="n">
         <v>12.4</v>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>586460.8</v>
+        <v>581864.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>682993.62</v>
+        <v>673751.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.48</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>711615.4</v>
+        <v>586460.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>672637.4</v>
+        <v>682993.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>611373.4</v>
+        <v>711615.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>693766.12</v>
+        <v>672637.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>819736</v>
+        <v>611373.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>697643.76</v>
+        <v>693766.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,269 +4454,269 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="AN10" t="n">
         <v>12.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>4292462.587606837</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>819736</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>697643.76</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>19.56</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>4297785.286733238</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>1155730.6</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>760224.08</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>10.63</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>19.82</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,42 +4884,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4928,19 +4928,19 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1178368.2</v>
+        <v>1155730.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>758152.4399999999</v>
+        <v>760224.08</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>102422.5752553308</t>
+          <t>30095.86714513553</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,142 +5016,142 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>19.56</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>12.35</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>10.63</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>19.82</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>12.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,54 +5314,54 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>12.44</v>
+        <v>12.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-80.76</t>
+          <t>-37.02</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.64</t>
+          <t>-104.01</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4297785.286733238</t>
+          <t>4292462.587606837</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>98400.0</t>
+          <t>1361673.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>983189.6</v>
+        <v>1178368.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>768634.0</t>
+          <t>876208.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>737617.34</v>
+        <v>758152.4399999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>214555</t>
+          <t>302159</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>30614.82493160136</t>
+          <t>41662.17113525204</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>74825.17343934788</t>
+          <t>102422.5752553308</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>98400.0</t>
+          <t>1361673.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,17 +5446,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>2.626</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,64 +5628,64 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>39.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-25.58</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-20.05</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>38.65</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -5749,63 +5749,63 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.68</v>
+        <v>38.75</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.27</v>
+        <v>38.3</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.11</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-24.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-90.01</t>
+          <t>-90.03</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>561024.2</v>
+        <v>414142.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>701706.1</t>
+          <t>556495.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>840829.2</v>
+        <v>839834.6800000001</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-140681</t>
+          <t>-142352</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-39784.70197289828</t>
+          <t>-57394.19364341711</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-129016.5672358562</t>
+          <t>-154246.3978312707</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.017</t>
+          <t>1.723</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,79 +6058,79 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-20.05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>38.7</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-29.71</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>37.85</t>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6194,17 +6194,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6214,179 +6214,179 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.65</v>
+        <v>38.68</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.25</v>
+        <v>38.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-24.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-90.01</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>5077340.122478386</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>561024.2</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>701706.1</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>840829.2</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-140681</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-39784.70197289828</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-129016.5672358562</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-89.40</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>5084444.435064935</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>619199.2</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>880917.9</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>853954.26</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-261718</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-23560.72647054229</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-84443.28898398345</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>24.017</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-45.70</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.61</v>
+        <v>38.65</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.24</v>
+        <v>38.25</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-89.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>635547.8</v>
+        <v>619199.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1170372.0</t>
+          <t>880917.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>848534.38</v>
+        <v>853954.26</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-534824</t>
+          <t>-261718</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-12491.16964991662</t>
+          <t>-23560.72647054229</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-109434.3454461659</t>
+          <t>-84443.28898398345</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.707</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,72 +6918,72 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-45.70</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>38.65</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-44.84</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -6998,32 +6998,32 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>0.13</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>0.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,214 +7039,214 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.57</v>
+        <v>38.61</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.23</v>
+        <v>38.24</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-88.98</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>5077340.122478386</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>635547.8</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>1170372.0</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>848534.38</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-534824</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-12491.16964991662</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-109434.3454461659</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-88.76</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>5084444.435064935</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>641872.8</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>1163713.7</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>872957</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-521840</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>5134.862313037787</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-70260.4494833491</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,107 +7333,107 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-44.84</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>21.509</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-40.58</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,17 +7469,17 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -7489,43 +7489,43 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>38.54</v>
+        <v>38.57</v>
       </c>
       <c r="AN17" t="n">
         <v>38.23</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-88.76</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>698847.6</v>
+        <v>641872.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1176139.7</t>
+          <t>1163713.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>885973</v>
+        <v>872957</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-477292</t>
+          <t>-521840</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>18843.10082147177</t>
+          <t>5134.862313037787</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-61208.83205491968</t>
+          <t>-70260.4494833491</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>21.509</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,14 +7858,14 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,63 +7899,63 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>38.5</v>
+        <v>38.54</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.21</v>
+        <v>38.23</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>842388</v>
+        <v>698847.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>880787.42</v>
+        <v>885973</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,78 +8329,78 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-89.57</t>
+          <t>-88.95</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>1142636.6</v>
+        <v>842388</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1168318.6</t>
+          <t>1102204.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>889614.54</v>
+        <v>880787.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-25682</t>
+          <t>-259816</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>50118.57370920612</t>
+          <t>33397.9977080884</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1252.468849041965</t>
+          <t>-58565.17029805912</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>38.42</v>
+        <v>38.46</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.18</v>
+        <v>38.2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1705196.2</v>
+        <v>1142636.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1168996.3</t>
+          <t>1168318.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>888941.14</v>
+        <v>889614.54</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>-25682</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>59458.76326525123</t>
+          <t>50118.57370920612</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>11391.54996559117</t>
+          <t>-1252.468849041965</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>38.36</v>
+        <v>38.42</v>
       </c>
       <c r="AN21" t="n">
-        <v>38.15</v>
+        <v>38.18</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1685554.6</v>
+        <v>1705196.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>908619.58</v>
+        <v>888941.14</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>38.27</v>
+        <v>38.36</v>
       </c>
       <c r="AN22" t="n">
-        <v>38.12</v>
+        <v>38.15</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1653431.8</v>
+        <v>1685554.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>899236.42</v>
+        <v>908619.58</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>159341.9915172313</t>
+          <t>105384.4143448677</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.361</t>
+          <t>39.165</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>38.18</v>
+        <v>38.27</v>
       </c>
       <c r="AN23" t="n">
-        <v>38.09</v>
+        <v>38.12</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>119.37</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-94.16</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5084444.435064935</t>
+          <t>5077340.122478386</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1362021</v>
+        <v>1653431.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1090324.2</t>
+          <t>1218436.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>886390.3</v>
+        <v>899236.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>271696</t>
+          <t>434994</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>43636.25436182194</t>
+          <t>61437.1370011157</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>171885.7806378498</t>
+          <t>159341.9915172313</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1858205.0</t>
+          <t>1554812.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.123</t>
+          <t>103.792</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,38 +993,38 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.5</v>
+        <v>12.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>188.02</t>
+          <t>126.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-88.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>374167.0</t>
+          <t>1345892.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>547969.4</v>
+        <v>786967.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>567215.1</t>
+          <t>684416.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>665566.54</v>
+        <v>685318.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-19245</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5194.13927403183</t>
+          <t>-2679.034177245515</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-52544.98789529642</t>
+          <t>11154.04385507922</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>374167.0</t>
+          <t>1345892.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.251</t>
+          <t>28.123</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,74 +1328,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-3.39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-6.85</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>12.8</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>94.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>372.73</t>
+          <t>188.02</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.94</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>620316</v>
+        <v>547969.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>665965.7</t>
+          <t>567215.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>675357.36</v>
+        <v>665566.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-45649</t>
+          <t>-19245</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3415.10592983446</t>
+          <t>-5194.13927403183</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-37553.60511385801</t>
+          <t>-52544.98789529642</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>13.1</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>13.65</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30.294</t>
+          <t>22.251</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1874,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.44</v>
+        <v>12.47</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4653.53</t>
+          <t>372.73</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.72</t>
+          <t>-95.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>680506.4</v>
+        <v>620316</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>645939.9</t>
+          <t>665965.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>682702.16</v>
+        <v>675357.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>-45649</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>10863.96248323309</t>
+          <t>3415.10592983446</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-6705.893814879702</t>
+          <t>-37553.60511385801</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,127 +2173,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>30.294</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>113.361</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.92</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>12.38</v>
+        <v>12.42</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>4653.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.95</t>
+          <t>-99.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>756661.6</v>
+        <v>680506.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>788198.8</t>
+          <t>645939.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>690434.86</v>
+        <v>682702.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-31537</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>14058.48181016269</t>
+          <t>10863.96248323309</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>26112.93996276357</t>
+          <t>-6705.893814879702</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>113.361</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,87 +2618,87 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-33.03</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>12.32</v>
+        <v>12.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>296.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-102.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>581864.4</v>
+        <v>756661.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>868797.5</t>
+          <t>788198.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>673751.64</v>
+        <v>690434.86</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-286933</t>
+          <t>-31537</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>11866.76214605344</t>
+          <t>14058.48181016269</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-46258.61678213044</t>
+          <t>26112.93996276357</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,51 +3164,51 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="AN7" t="n">
         <v>12.4</v>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>586460.8</v>
+        <v>581864.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>682993.62</v>
+        <v>673751.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>711615.4</v>
+        <v>586460.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>672637.4</v>
+        <v>682993.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>611373.4</v>
+        <v>711615.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>693766.12</v>
+        <v>672637.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>819736</v>
+        <v>611373.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>697643.76</v>
+        <v>693766.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,269 +4884,269 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="AN11" t="n">
         <v>12.43</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>4289228.413229018</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>819736</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>697643.76</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>19.54</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>4292462.587606837</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>1155730.6</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>760224.08</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-7.14</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>10.47</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>14.031</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,42 +5314,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5358,19 +5358,19 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>-18.70</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.01</t>
+          <t>-104.20</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4292462.587606837</t>
+          <t>4289228.413229018</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1178368.2</v>
+        <v>1155730.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>876208.7</t>
+          <t>846170.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>758152.4399999999</v>
+        <v>760224.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>302159</t>
+          <t>309560</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>41662.17113525204</t>
+          <t>39882.73975215718</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>102422.5752553308</t>
+          <t>30095.86714513553</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1361673.0</t>
+          <t>173882.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>9.087</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-30.68</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,37 +5744,37 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5784,136 +5784,136 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.75</v>
+        <v>38.79</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.3</v>
+        <v>38.32</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-90.30</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>5070795.192086331</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>352409.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>340485.6</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>491179.2</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>818119</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-150693</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-71537.08989862665</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-149323.0193022791</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>352409.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
         <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-90.03</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>5077340.122478386</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>102701.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>414142.4</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>556495.0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>839834.6800000001</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-142352</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-57394.19364341711</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-154246.3978312707</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>102701.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
       <c r="BN13" t="inlineStr">
         <is>
           <t>-59.62418527250035</t>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>2.626</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,64 +6058,64 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>39.6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-25.58</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-20.05</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>38.65</t>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.68</v>
+        <v>38.75</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.27</v>
+        <v>38.3</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.11</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-24.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-90.01</t>
+          <t>-90.03</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>561024.2</v>
+        <v>414142.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>701706.1</t>
+          <t>556495.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>840829.2</v>
+        <v>839834.6800000001</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-140681</t>
+          <t>-142352</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-39784.70197289828</t>
+          <t>-57394.19364341711</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-129016.5672358562</t>
+          <t>-154246.3978312707</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24.017</t>
+          <t>1.723</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,79 +6488,79 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-20.05</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>38.7</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-29.71</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>37.85</t>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,17 +6604,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6624,17 +6624,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,179 +6644,179 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.65</v>
+        <v>38.68</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.25</v>
+        <v>38.27</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-24.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-90.01</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>5070795.192086331</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>561024.2</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>701706.1</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>840829.2</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-140681</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-39784.70197289828</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-129016.5672358562</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-89.40</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>5077340.122478386</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>619199.2</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>880917.9</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>853954.26</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-261718</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-23560.72647054229</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-84443.28898398345</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>24.017</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-45.70</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.61</v>
+        <v>38.65</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.24</v>
+        <v>38.25</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-89.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>635547.8</v>
+        <v>619199.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1170372.0</t>
+          <t>880917.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>848534.38</v>
+        <v>853954.26</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-534824</t>
+          <t>-261718</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-12491.16964991662</t>
+          <t>-23560.72647054229</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-109434.3454461659</t>
+          <t>-84443.28898398345</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.707</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,72 +7348,72 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-45.70</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>38.65</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-44.84</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7428,32 +7428,32 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>0.13</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>0.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,219 +7464,219 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>38.57</v>
+        <v>38.61</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.23</v>
+        <v>38.24</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-88.98</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>5070795.192086331</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>635547.8</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>1170372.0</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>848534.38</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-534824</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-12491.16964991662</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-109434.3454461659</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-88.76</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>5077340.122478386</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>641872.8</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>1163713.7</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>872957</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>-521840</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>5134.862313037787</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>-70260.4494833491</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,107 +7763,107 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-44.84</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>21.509</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-40.58</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,22 +7894,22 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -7919,43 +7919,43 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>38.54</v>
+        <v>38.57</v>
       </c>
       <c r="AN18" t="n">
         <v>38.23</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-88.76</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>698847.6</v>
+        <v>641872.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1176139.7</t>
+          <t>1163713.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>885973</v>
+        <v>872957</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-477292</t>
+          <t>-521840</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>18843.10082147177</t>
+          <t>5134.862313037787</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-61208.83205491968</t>
+          <t>-70260.4494833491</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>21.509</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,14 +8288,14 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,68 +8324,68 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>38.5</v>
+        <v>38.54</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.21</v>
+        <v>38.23</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>842388</v>
+        <v>698847.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>880787.42</v>
+        <v>885973</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,83 +8754,83 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM20" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-89.57</t>
+          <t>-88.95</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1142636.6</v>
+        <v>842388</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1168318.6</t>
+          <t>1102204.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>889614.54</v>
+        <v>880787.42</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-25682</t>
+          <t>-259816</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>50118.57370920612</t>
+          <t>33397.9977080884</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1252.468849041965</t>
+          <t>-58565.17029805912</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>38.42</v>
+        <v>38.46</v>
       </c>
       <c r="AN21" t="n">
-        <v>38.18</v>
+        <v>38.2</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-89.57</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1705196.2</v>
+        <v>1142636.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1168996.3</t>
+          <t>1168318.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>888941.14</v>
+        <v>889614.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>-25682</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>59458.76326525123</t>
+          <t>50118.57370920612</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>11391.54996559117</t>
+          <t>-1252.468849041965</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>291061.0</t>
+          <t>1003538.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>38.36</v>
+        <v>38.42</v>
       </c>
       <c r="AN22" t="n">
-        <v>38.15</v>
+        <v>38.18</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1685554.6</v>
+        <v>1705196.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>908619.58</v>
+        <v>888941.14</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>39.165</t>
+          <t>25.281</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>38.27</v>
+        <v>38.36</v>
       </c>
       <c r="AN23" t="n">
-        <v>38.12</v>
+        <v>38.15</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>96.73</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.16</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5077340.122478386</t>
+          <t>5070795.192086331</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1653431.8</v>
+        <v>1685554.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1218436.9</t>
+          <t>1231296.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>899236.42</v>
+        <v>908619.58</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>434994</t>
+          <t>454257</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>61437.1370011157</t>
+          <t>68198.25659246216</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>159341.9915172313</t>
+          <t>105384.4143448677</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1554812.0</t>
+          <t>1005567.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>103.792</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.62</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>12.56</v>
+        <v>12.61</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.52</v>
+        <v>12.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>126.08</t>
+          <t>73.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.80</t>
+          <t>-86.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1345892.0</t>
+          <t>264199.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>786967.8</v>
+        <v>537760.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>684416.1</t>
+          <t>647211.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>685318.88</v>
+        <v>683347.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>102551</t>
+          <t>-109450</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2679.034177245515</t>
+          <t>-6214.945844751574</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11154.04385507922</t>
+          <t>-25662.46001603489</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1345892.0</t>
+          <t>264199.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.123</t>
+          <t>103.792</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,38 +1423,38 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>12.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>188.02</t>
+          <t>126.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-88.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>374167.0</t>
+          <t>1345892.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>547969.4</v>
+        <v>786967.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>567215.1</t>
+          <t>684416.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>665566.54</v>
+        <v>685318.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-19245</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5194.13927403183</t>
+          <t>-2679.034177245515</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-52544.98789529642</t>
+          <t>11154.04385507922</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>374167.0</t>
+          <t>1345892.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.251</t>
+          <t>28.123</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,74 +1758,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-3.39</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-6.85</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>12.8</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>94.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>372.73</t>
+          <t>188.02</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-95.94</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>620316</v>
+        <v>547969.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>665965.7</t>
+          <t>567215.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>675357.36</v>
+        <v>665566.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-45649</t>
+          <t>-19245</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3415.10592983446</t>
+          <t>-5194.13927403183</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-37553.60511385801</t>
+          <t>-52544.98789529642</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>13.1</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>13.65</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.294</t>
+          <t>22.251</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,17 +2304,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.44</v>
+        <v>12.47</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4653.53</t>
+          <t>372.73</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-99.72</t>
+          <t>-95.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>680506.4</v>
+        <v>620316</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>645939.9</t>
+          <t>665965.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>682702.16</v>
+        <v>675357.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>-45649</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>10863.96248323309</t>
+          <t>3415.10592983446</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-6705.893814879702</t>
+          <t>-37553.60511385801</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,127 +2603,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30.294</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-3.46</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>113.361</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.92</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>12.38</v>
+        <v>12.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>4653.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.95</t>
+          <t>-99.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>756661.6</v>
+        <v>680506.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>788198.8</t>
+          <t>645939.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>690434.86</v>
+        <v>682702.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-31537</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>14058.48181016269</t>
+          <t>10863.96248323309</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>26112.93996276357</t>
+          <t>-6705.893814879702</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>113.361</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,87 +3048,87 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-3.85</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>6.69</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-33.03</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>12.32</v>
+        <v>12.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>296.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-102.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>581864.4</v>
+        <v>756661.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>868797.5</t>
+          <t>788198.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>673751.64</v>
+        <v>690434.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-286933</t>
+          <t>-31537</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>11866.76214605344</t>
+          <t>14058.48181016269</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-46258.61678213044</t>
+          <t>26112.93996276357</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,51 +3594,51 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="AN8" t="n">
         <v>12.4</v>
@@ -3650,12 +3650,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>586460.8</v>
+        <v>581864.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>682993.62</v>
+        <v>673751.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>711615.4</v>
+        <v>586460.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>672637.4</v>
+        <v>682993.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>611373.4</v>
+        <v>711615.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>693766.12</v>
+        <v>672637.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4289228.413229018</t>
+          <t>4283698.683238637</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>819736</v>
+        <v>611373.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>697643.76</v>
+        <v>693766.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.031</t>
+          <t>52.008</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,269 +5314,269 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="AN12" t="n">
         <v>12.43</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>12.36</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-6.31</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-104.27</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>4283698.683238637</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>819736</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>869479.2</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>697643.76</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-49743</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>35807.28745019002</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>13392.29978937062</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>636249.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>建材營造</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>213.791452172872</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>8.617367341441684</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-24.41489498891521</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>10.24</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>24.23%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>怡華-建材營造-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>12.35</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-18.70</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-104.20</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>4289228.413229018</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>1155730.6</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>846170.0</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>760224.08</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>309560</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>39882.73975215718</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>30095.86714513553</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>173882.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-7.14</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>怡華</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>建材營造</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>213.791452172872</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>8.617367341441684</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-24.41489498891521</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>10.59</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>24.23%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>19.54</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>不動產部-商品銷售79.54%、紡織部-加工13.46%、不動產租賃6.98%、紡織部-商品銷售0.02% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>怡華-建材營造-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.087</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-30.68</t>
+          <t>-33.10</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.79</v>
+        <v>38.83</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.32</v>
+        <v>38.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-23.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-90.30</t>
+          <t>-90.85</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>352409.0</t>
+          <t>154187.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>340485.6</v>
+        <v>319435.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>491179.2</t>
+          <t>477491.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>818119</v>
+        <v>815212.14</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-150693</t>
+          <t>-158056</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-71537.08989862665</t>
+          <t>-84686.80358336533</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-149323.0193022791</t>
+          <t>-157010.228849428</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>352409.0</t>
+          <t>154187.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
+          <t>38.35</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>38.6</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>38.75</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>9.087</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-30.68</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,32 +6179,32 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6214,35 +6214,35 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.75</v>
+        <v>38.79</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.3</v>
+        <v>38.32</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-90.03</t>
+          <t>-90.30</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>102701.0</t>
+          <t>352409.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>414142.4</v>
+        <v>340485.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>556495.0</t>
+          <t>491179.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>839834.6800000001</v>
+        <v>818119</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-142352</t>
+          <t>-150693</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-57394.19364341711</t>
+          <t>-71537.08989862665</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-154246.3978312707</t>
+          <t>-149323.0193022791</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>102701.0</t>
+          <t>352409.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>2.626</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,64 +6488,64 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>39.6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-2.59</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-25.58</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-20.05</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>38.65</t>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -6609,63 +6609,63 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.68</v>
+        <v>38.75</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.27</v>
+        <v>38.3</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.11</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-24.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-90.01</t>
+          <t>-90.03</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>561024.2</v>
+        <v>414142.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>701706.1</t>
+          <t>556495.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>840829.2</v>
+        <v>839834.6800000001</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-140681</t>
+          <t>-142352</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-39784.70197289828</t>
+          <t>-57394.19364341711</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-129016.5672358562</t>
+          <t>-154246.3978312707</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.017</t>
+          <t>1.723</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,79 +6918,79 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-20.05</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>38.7</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-29.71</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>37.85</t>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7074,179 +7074,179 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.65</v>
+        <v>38.68</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.25</v>
+        <v>38.27</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-24.69</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-90.01</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>5063841.86637931</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>561024.2</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>701706.1</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>840829.2</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-140681</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-39784.70197289828</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-129016.5672358562</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>66087.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-89.40</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>5070795.192086331</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>619199.2</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>880917.9</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>853954.26</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-261718</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-23560.72647054229</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-84443.28898398345</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>921795.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>24.017</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-45.70</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>38.61</v>
+        <v>38.65</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.24</v>
+        <v>38.25</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-89.40</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>635547.8</v>
+        <v>619199.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1170372.0</t>
+          <t>880917.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>848534.38</v>
+        <v>853954.26</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-534824</t>
+          <t>-261718</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-12491.16964991662</t>
+          <t>-23560.72647054229</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-109434.3454461659</t>
+          <t>-84443.28898398345</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>259436.0</t>
+          <t>921795.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18.707</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,72 +7778,72 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-45.70</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>38.65</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-44.84</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7858,32 +7858,32 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
           <t>0.13</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>0.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,214 +7899,214 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>38.57</v>
+        <v>38.61</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.23</v>
+        <v>38.24</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-88.98</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>5063841.86637931</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>635547.8</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>1170372.0</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>848534.38</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-534824</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-12491.16964991662</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-109434.3454461659</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>259436.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-59.62418527250035</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>18.25751421608448</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>-21.80315938182285</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-88.76</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>5070795.192086331</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>641872.8</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>1163713.7</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>872957</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-521840</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>5134.862313037787</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>-70260.4494833491</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>720693.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-59.62418527250035</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>18.25751421608448</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>-21.80315938182285</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8193,107 +8193,107 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-44.84</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>21.509</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-40.58</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -8349,43 +8349,43 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>38.54</v>
+        <v>38.57</v>
       </c>
       <c r="AN19" t="n">
         <v>38.23</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-88.76</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>698847.6</v>
+        <v>641872.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1176139.7</t>
+          <t>1163713.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>885973</v>
+        <v>872957</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-477292</t>
+          <t>-521840</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>18843.10082147177</t>
+          <t>5134.862313037787</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-61208.83205491968</t>
+          <t>-70260.4494833491</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>837110.0</t>
+          <t>720693.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>21.509</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-40.58</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,14 +8718,14 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,63 +8759,63 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>38.5</v>
+        <v>38.54</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.21</v>
+        <v>38.23</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-88.66</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>842388</v>
+        <v>698847.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1102204.5</t>
+          <t>1176139.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>880787.42</v>
+        <v>885973</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-259816</t>
+          <t>-477292</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>33397.9977080884</t>
+          <t>18843.10082147177</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-58565.17029805912</t>
+          <t>-61208.83205491968</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>356962.0</t>
+          <t>837110.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.962</t>
+          <t>9.315</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,78 +9189,78 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>53.89</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>39.23999999999999</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>38.03</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>22.58</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>39.32000000000001</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-89.57</t>
+          <t>-88.95</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1142636.6</v>
+        <v>842388</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1168318.6</t>
+          <t>1102204.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>889614.54</v>
+        <v>880787.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-25682</t>
+          <t>-259816</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>50118.57370920612</t>
+          <t>33397.9977080884</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1252.468849041965</t>
+          <t>-58565.17029805912</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1003538.0</t>
+          <t>356962.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>25.962</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>45.87</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,171 +9619,171 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>38.42</v>
+        <v>38.46</v>
       </c>
       <c r="AN22" t="n">
-        <v>38.18</v>
+        <v>38.2</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-89.57</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>5063841.86637931</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>1003538.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>1142636.6</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>1168318.6</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>889614.54</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-25682</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>50118.57370920612</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-1252.468849041965</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1003538.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-90.69</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>5070795.192086331</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>291061.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>1705196.2</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>1168996.3</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>888941.14</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>536199</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>59458.76326525123</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>11391.54996559117</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>291061.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
       <c r="BN22" t="inlineStr">
         <is>
           <t>-59.62418527250035</t>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>7.337</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>45.87</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>38.36</v>
+        <v>38.42</v>
       </c>
       <c r="AN23" t="n">
-        <v>38.15</v>
+        <v>38.18</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>96.73</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>5070795.192086331</t>
+          <t>5063841.86637931</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1685554.6</v>
+        <v>1705196.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1231296.9</t>
+          <t>1168996.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>908619.58</v>
+        <v>888941.14</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>454257</t>
+          <t>536199</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>68198.25659246216</t>
+          <t>59458.76326525123</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>105384.4143448677</t>
+          <t>11391.54996559117</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1005567.0</t>
+          <t>291061.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
+++ b/Result/checksun_type/天然纖維產品(例如純棉、純羊毛等).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>11.017</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,104 +993,104 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>81.51</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>12.43</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>13.34</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>73.83</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.27</t>
+          <t>-84.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>264199.0</t>
+          <t>145321.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>537760.6</v>
+        <v>485647.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>647211.1</t>
+          <t>583076.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>683347.38</v>
+        <v>664557.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-109450</t>
+          <t>-97429</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6214.945844751574</t>
+          <t>-14444.69282639193</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-25662.46001603489</t>
+          <t>-59708.30122541392</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>264199.0</t>
+          <t>145321.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>103.792</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.62</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>12.56</v>
+        <v>12.61</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.52</v>
+        <v>12.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>126.08</t>
+          <t>73.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.80</t>
+          <t>-86.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1345892.0</t>
+          <t>264199.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>786967.8</v>
+        <v>537760.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>684416.1</t>
+          <t>647211.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>685318.88</v>
+        <v>683347.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>102551</t>
+          <t>-109450</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2679.034177245515</t>
+          <t>-6214.945844751574</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11154.04385507922</t>
+          <t>-25662.46001603489</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1345892.0</t>
+          <t>264199.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28.123</t>
+          <t>103.792</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,38 +1853,38 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.5</v>
+        <v>12.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>188.02</t>
+          <t>126.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-88.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>374167.0</t>
+          <t>1345892.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>547969.4</v>
+        <v>786967.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>567215.1</t>
+          <t>684416.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>665566.54</v>
+        <v>685318.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-19245</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5194.13927403183</t>
+          <t>-2679.034177245515</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-52544.98789529642</t>
+          <t>11154.04385507922</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>374167.0</t>
+          <t>1345892.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.251</t>
+          <t>28.123</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,74 +2188,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-3.39</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-3.85</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-6.85</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>12.8</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>94.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>372.73</t>
+          <t>188.02</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-95.94</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>620316</v>
+        <v>547969.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>665965.7</t>
+          <t>567215.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>675357.36</v>
+        <v>665566.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-45649</t>
+          <t>-19245</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3415.10592983446</t>
+          <t>-5194.13927403183</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-37553.60511385801</t>
+          <t>-52544.98789529642</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>298658.0</t>
+          <t>374167.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>13.1</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>13.65</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30.294</t>
+          <t>22.251</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>96.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.44</v>
+        <v>12.47</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4653.53</t>
+          <t>372.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-99.72</t>
+          <t>-95.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>680506.4</v>
+        <v>620316</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>645939.9</t>
+          <t>665965.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>682702.16</v>
+        <v>675357.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>-45649</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>10863.96248323309</t>
+          <t>3415.10592983446</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-6705.893814879702</t>
+          <t>-37553.60511385801</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>405887.0</t>
+          <t>298658.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,127 +3033,127 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>30.294</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>113.361</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-3.85</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.77</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>98.92</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>12.38</v>
+        <v>12.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>4653.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.95</t>
+          <t>-99.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>756661.6</v>
+        <v>680506.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>788198.8</t>
+          <t>645939.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>690434.86</v>
+        <v>682702.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-31537</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>14058.48181016269</t>
+          <t>10863.96248323309</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>26112.93996276357</t>
+          <t>-6705.893814879702</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1510235.0</t>
+          <t>405887.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>113.361</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,87 +3478,87 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-33.03</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>12.32</v>
+        <v>12.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>296.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-102.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>581864.4</v>
+        <v>756661.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>868797.5</t>
+          <t>788198.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>673751.64</v>
+        <v>690434.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-286933</t>
+          <t>-31537</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>11866.76214605344</t>
+          <t>14058.48181016269</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-46258.61678213044</t>
+          <t>26112.93996276357</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>150900.0</t>
+          <t>1510235.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>12.55</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.54</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,51 +4024,51 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="AN9" t="n">
         <v>12.4</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.35</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>586460.8</v>
+        <v>581864.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>882414.5</t>
+          <t>868797.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>682993.62</v>
+        <v>673751.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-295953</t>
+          <t>-286933</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>22435.01286026869</t>
+          <t>11866.76214605344</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2351.425818331423</t>
+          <t>-46258.61678213044</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>735900.0</t>
+          <t>150900.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.752</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-33.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>12.34</v>
+        <v>12.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.41</v>
+        <v>12.4</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-49.33</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>711615.4</v>
+        <v>586460.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>847402.5</t>
+          <t>882414.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>672637.4</v>
+        <v>682993.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-135787</t>
+          <t>-295953</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>26941.63807455963</t>
+          <t>22435.01286026869</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2221.459233678179</t>
+          <t>-2351.425818331423</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>599610.0</t>
+          <t>735900.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>64.202</t>
+          <t>49.752</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>12.38</v>
+        <v>12.34</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-49.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>611373.4</v>
+        <v>711615.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>892411.1</t>
+          <t>847402.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>693766.12</v>
+        <v>672637.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-281037</t>
+          <t>-135787</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32244.01940333013</t>
+          <t>26941.63807455963</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>12646.0451456008</t>
+          <t>-2221.459233678179</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>786663.0</t>
+          <t>599610.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>12.15</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.008</t>
+          <t>64.202</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,54 +5314,54 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.27</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4283698.683238637</t>
+          <t>4277931.708510638</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>819736</v>
+        <v>611373.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>869479.2</t>
+          <t>892411.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>697643.76</v>
+        <v>693766.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-49743</t>
+          <t>-281037</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35807.28745019002</t>
+          <t>32244.01940333013</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>13392.29978937062</t>
+          <t>12646.0451456008</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>636249.0</t>
+          <t>786663.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.471</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,64 +5628,64 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-49.57</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-33.10</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>38.65</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>38.83</v>
+        <v>38.87</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.33</v>
+        <v>38.36</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-23.74</t>
+          <t>-21.04</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-90.85</t>
+          <t>-91.30</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>5063841.86637931</t>
+          <t>5057369.670731707</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>154187.0</t>
+          <t>368481.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>319435.8</v>
+        <v>208773</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>477491.8</t>
+          <t>413986.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>815212.14</v>
+        <v>821071.24</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-158056</t>
+          <t>-205213</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-84686.80358336533</t>
+          <t>-93564.82915687781</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-157010.228849428</t>
+          <t>-142393.9698111964</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>154187.0</t>
+          <t>368481.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.087</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-30.68</t>
+          <t>-33.10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6194,156 +6194,156 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>38.79</v>
+        <v>38.83</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.32</v>
+        <v>38.33</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-23.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-90.85</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>5057369.670731707</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>154187.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>319435.8</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>477491.8</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>815212.14</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-158056</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-84686.80358336533</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-157010.228849428</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>154187.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-90.30</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>5063841.86637931</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>352409.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>340485.6</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>491179.2</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>818119</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-150693</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-71537.08989862665</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-149323.0193022791</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>352409.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
       <c r="BN14" t="inlineStr">
         <is>
           <t>-59.62418527250035</t>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
+          <t>38.35</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>38.6</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>38.75</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>9.087</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-30.68</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,32 +6609,32 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,136 +6644,136 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>38.75</v>
+        <v>38.79</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.3</v>
+        <v>38.32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-90.30</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>5057369.670731707</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>352409.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>340485.6</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>491179.2</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>818119</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-150693</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-71537.08989862665</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-149323.0193022791</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>352409.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>紡織纖維</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
         <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-90.03</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>5063841.86637931</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>102701.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>414142.4</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>556495.0</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>839834.6800000001</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-142352</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-57394.19364341711</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-154246.3978312707</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>102701.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>紡織纖維</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
       <c r="BN15" t="inlineStr">
         <is>
           <t>-59.62418527250035</t>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>2.626</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,64 +6918,64 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>39.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-25.58</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-20.05</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>38.65</t>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -7039,63 +7039,63 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.68</v>
+        <v>38.75</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.27</v>
+        <v>38.3</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.11</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-24.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-90.01</t>
+          <t>-90.03</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5063841.86637931</t>
+          <t>5057369.670731707</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>561024.2</v>
+        <v>414142.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>701706.1</t>
+          <t>556495.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>840829.2</v>
+        <v>839834.6800000001</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-140681</t>
+          <t>-142352</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-39784.70197289828</t>
+          <t>-57394.19364341711</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-129016.5672358562</t>
+          <t>-154246.3978312707</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>66087.0</t>
+          <t>102701.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24.017</t>
+          <t>1.723</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,79 +7348,79 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-20.05</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>38.7</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-29.71</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>37.85</t>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
     